--- a/PLANILHA FÁBRICA DE GELO att1.xlsx
+++ b/PLANILHA FÁBRICA DE GELO att1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vipriosaude-my.sharepoint.com/personal/renata_stavale_klinisaude_com_br/Documents/Área de Trabalho/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vipriosaude-my.sharepoint.com/personal/enzo_romana_klinisaude_com_br/Documents/Área de Trabalho/Guia_update/WR_Gelo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1152" documentId="8_{EE42E74A-96BB-461F-8E91-BDCBBDD5BCB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A1577C1-5775-46A1-BC8B-8F4FEA3783FE}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{F6D3F216-703C-4A95-8F2B-DEA827CC7586}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{284B1DFE-83CB-403E-B3CE-7D363879E545}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{E253E163-9AA6-422B-96B3-2C5FC4F9EADA}"/>
   </bookViews>
@@ -1020,15 +1020,6 @@
     <xf numFmtId="44" fontId="2" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
@@ -1038,10 +1029,13 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1055,6 +1049,12 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1072,10 +1072,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1414,28 +1410,28 @@
     <col min="15" max="15" width="17.36328125" style="1" customWidth="1"/>
     <col min="16" max="16" width="8.7265625" style="1"/>
     <col min="17" max="17" width="17.81640625" style="1" customWidth="1"/>
-    <col min="18" max="18" width="10.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.90625" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:18" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="79"/>
+      <c r="B1" s="75" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="77"/>
       <c r="F1" s="9"/>
-      <c r="H1" s="69" t="s">
+      <c r="H1" s="72" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="70"/>
-      <c r="J1" s="70"/>
-      <c r="K1" s="70"/>
-      <c r="L1" s="70"/>
-      <c r="M1" s="70"/>
-      <c r="N1" s="70"/>
-      <c r="O1" s="71"/>
+      <c r="I1" s="73"/>
+      <c r="J1" s="73"/>
+      <c r="K1" s="73"/>
+      <c r="L1" s="73"/>
+      <c r="M1" s="73"/>
+      <c r="N1" s="73"/>
+      <c r="O1" s="74"/>
     </row>
     <row r="2" spans="2:18" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B2" s="3" t="s">
@@ -1451,7 +1447,7 @@
         <v>9</v>
       </c>
       <c r="F2" s="8"/>
-      <c r="G2" s="80" t="s">
+      <c r="G2" s="78" t="s">
         <v>12</v>
       </c>
       <c r="H2" s="47" t="s">
@@ -1494,7 +1490,7 @@
         <v>26743.029999999995</v>
       </c>
       <c r="F3" s="2"/>
-      <c r="G3" s="73"/>
+      <c r="G3" s="70"/>
       <c r="H3" s="30"/>
       <c r="I3" s="31">
         <v>12</v>
@@ -1531,7 +1527,7 @@
         <v>25908.029999999995</v>
       </c>
       <c r="F4" s="2"/>
-      <c r="G4" s="73"/>
+      <c r="G4" s="70"/>
       <c r="H4" s="24"/>
       <c r="I4" s="34">
         <v>1</v>
@@ -1572,7 +1568,7 @@
         <v>25908.029999999995</v>
       </c>
       <c r="F5" s="2"/>
-      <c r="G5" s="73"/>
+      <c r="G5" s="70"/>
       <c r="H5" s="24"/>
       <c r="I5" s="34">
         <v>5</v>
@@ -1597,10 +1593,10 @@
         <f t="shared" ref="O5:O24" si="2">O4+M5</f>
         <v>118</v>
       </c>
-      <c r="Q5" s="75" t="s">
+      <c r="Q5" s="79" t="s">
         <v>62</v>
       </c>
-      <c r="R5" s="76"/>
+      <c r="R5" s="80"/>
     </row>
     <row r="6" spans="2:18" ht="16" x14ac:dyDescent="0.35">
       <c r="B6" s="16" t="s">
@@ -1617,7 +1613,7 @@
         <v>25908.029999999995</v>
       </c>
       <c r="F6" s="2"/>
-      <c r="G6" s="73"/>
+      <c r="G6" s="70"/>
       <c r="H6" s="43">
         <v>46077</v>
       </c>
@@ -1666,7 +1662,7 @@
         <v>25908.029999999995</v>
       </c>
       <c r="F7" s="2"/>
-      <c r="G7" s="73"/>
+      <c r="G7" s="70"/>
       <c r="H7" s="43">
         <v>46077</v>
       </c>
@@ -1715,7 +1711,7 @@
         <v>25908.029999999995</v>
       </c>
       <c r="F8" s="2"/>
-      <c r="G8" s="73"/>
+      <c r="G8" s="70"/>
       <c r="H8" s="43">
         <v>46077</v>
       </c>
@@ -1764,7 +1760,7 @@
         <v>25908.029999999995</v>
       </c>
       <c r="F9" s="2"/>
-      <c r="G9" s="73"/>
+      <c r="G9" s="70"/>
       <c r="H9" s="43">
         <v>46078</v>
       </c>
@@ -1813,7 +1809,7 @@
         <v>25908.029999999995</v>
       </c>
       <c r="F10" s="2"/>
-      <c r="G10" s="73"/>
+      <c r="G10" s="70"/>
       <c r="H10" s="43">
         <v>46079</v>
       </c>
@@ -1863,7 +1859,7 @@
         <v>25908.029999999995</v>
       </c>
       <c r="F11" s="2"/>
-      <c r="G11" s="73"/>
+      <c r="G11" s="70"/>
       <c r="H11" s="43">
         <v>46079</v>
       </c>
@@ -1906,7 +1902,7 @@
         <v>25908.029999999995</v>
       </c>
       <c r="F12" s="2"/>
-      <c r="G12" s="73"/>
+      <c r="G12" s="70"/>
       <c r="H12" s="44">
         <v>46078</v>
       </c>
@@ -1947,7 +1943,7 @@
         <v>25908.029999999995</v>
       </c>
       <c r="F13" s="2"/>
-      <c r="G13" s="73"/>
+      <c r="G13" s="70"/>
       <c r="H13" s="44">
         <v>46078</v>
       </c>
@@ -1988,7 +1984,7 @@
         <v>25908.029999999995</v>
       </c>
       <c r="F14" s="2"/>
-      <c r="G14" s="73"/>
+      <c r="G14" s="70"/>
       <c r="H14" s="24"/>
       <c r="I14" s="34"/>
       <c r="J14" s="34"/>
@@ -2021,7 +2017,7 @@
         <v>25908.029999999995</v>
       </c>
       <c r="F15" s="2"/>
-      <c r="G15" s="73"/>
+      <c r="G15" s="70"/>
       <c r="H15" s="24"/>
       <c r="I15" s="34"/>
       <c r="J15" s="34"/>
@@ -2054,7 +2050,7 @@
         <v>25908.029999999995</v>
       </c>
       <c r="F16" s="2"/>
-      <c r="G16" s="73"/>
+      <c r="G16" s="70"/>
       <c r="H16" s="24"/>
       <c r="I16" s="34"/>
       <c r="J16" s="34"/>
@@ -2087,7 +2083,7 @@
         <v>25908.029999999995</v>
       </c>
       <c r="F17" s="2"/>
-      <c r="G17" s="73"/>
+      <c r="G17" s="70"/>
       <c r="H17" s="24"/>
       <c r="I17" s="34"/>
       <c r="J17" s="34"/>
@@ -2120,7 +2116,7 @@
         <v>25908.029999999995</v>
       </c>
       <c r="F18" s="2"/>
-      <c r="G18" s="73"/>
+      <c r="G18" s="70"/>
       <c r="H18" s="24"/>
       <c r="I18" s="34"/>
       <c r="J18" s="34"/>
@@ -2153,7 +2149,7 @@
         <v>25908.029999999995</v>
       </c>
       <c r="F19" s="2"/>
-      <c r="G19" s="73"/>
+      <c r="G19" s="70"/>
       <c r="H19" s="24"/>
       <c r="I19" s="34"/>
       <c r="J19" s="34"/>
@@ -2186,7 +2182,7 @@
         <v>25908.029999999995</v>
       </c>
       <c r="F20" s="2"/>
-      <c r="G20" s="73"/>
+      <c r="G20" s="70"/>
       <c r="H20" s="24"/>
       <c r="I20" s="34"/>
       <c r="J20" s="34"/>
@@ -2219,7 +2215,7 @@
         <v>25908.029999999995</v>
       </c>
       <c r="F21" s="2"/>
-      <c r="G21" s="73"/>
+      <c r="G21" s="70"/>
       <c r="H21" s="24"/>
       <c r="I21" s="34"/>
       <c r="J21" s="34"/>
@@ -2252,7 +2248,7 @@
         <v>25908.029999999995</v>
       </c>
       <c r="F22" s="2"/>
-      <c r="G22" s="73"/>
+      <c r="G22" s="70"/>
       <c r="H22" s="24"/>
       <c r="I22" s="34"/>
       <c r="J22" s="34"/>
@@ -2285,7 +2281,7 @@
         <v>25908.029999999995</v>
       </c>
       <c r="F23" s="2"/>
-      <c r="G23" s="73"/>
+      <c r="G23" s="70"/>
       <c r="H23" s="24"/>
       <c r="I23" s="34"/>
       <c r="J23" s="34"/>
@@ -2318,7 +2314,7 @@
         <v>25908.029999999995</v>
       </c>
       <c r="F24" s="2"/>
-      <c r="G24" s="74"/>
+      <c r="G24" s="71"/>
       <c r="H24" s="36"/>
       <c r="I24" s="37"/>
       <c r="J24" s="37"/>
@@ -2428,16 +2424,16 @@
         <f t="shared" si="1"/>
         <v>25908.029999999995</v>
       </c>
-      <c r="H28" s="69" t="s">
+      <c r="H28" s="72" t="s">
         <v>44</v>
       </c>
-      <c r="I28" s="70"/>
-      <c r="J28" s="70"/>
-      <c r="K28" s="70"/>
-      <c r="L28" s="70"/>
-      <c r="M28" s="70"/>
-      <c r="N28" s="70"/>
-      <c r="O28" s="71"/>
+      <c r="I28" s="73"/>
+      <c r="J28" s="73"/>
+      <c r="K28" s="73"/>
+      <c r="L28" s="73"/>
+      <c r="M28" s="73"/>
+      <c r="N28" s="73"/>
+      <c r="O28" s="74"/>
     </row>
     <row r="29" spans="2:18" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B29" s="6"/>
@@ -2451,7 +2447,7 @@
         <f t="shared" si="1"/>
         <v>25908.029999999995</v>
       </c>
-      <c r="G29" s="72" t="s">
+      <c r="G29" s="69" t="s">
         <v>15</v>
       </c>
       <c r="H29" s="56" t="s">
@@ -2491,7 +2487,7 @@
         <f t="shared" si="1"/>
         <v>25908.029999999995</v>
       </c>
-      <c r="G30" s="73"/>
+      <c r="G30" s="70"/>
       <c r="H30" s="53">
         <v>46083</v>
       </c>
@@ -2531,7 +2527,7 @@
         <f t="shared" si="1"/>
         <v>25908.029999999995</v>
       </c>
-      <c r="G31" s="73"/>
+      <c r="G31" s="70"/>
       <c r="H31" s="53">
         <v>46083</v>
       </c>
@@ -2558,10 +2554,10 @@
         <f>O30+M31-N31</f>
         <v>339.5</v>
       </c>
-      <c r="Q31" s="75" t="s">
+      <c r="Q31" s="79" t="s">
         <v>63</v>
       </c>
-      <c r="R31" s="76"/>
+      <c r="R31" s="80"/>
     </row>
     <row r="32" spans="2:18" ht="16" x14ac:dyDescent="0.35">
       <c r="B32" s="6"/>
@@ -2575,7 +2571,7 @@
         <f t="shared" si="1"/>
         <v>25908.029999999995</v>
       </c>
-      <c r="G32" s="73"/>
+      <c r="G32" s="70"/>
       <c r="H32" s="53">
         <v>46083</v>
       </c>
@@ -2621,7 +2617,7 @@
         <f t="shared" si="1"/>
         <v>25908.029999999995</v>
       </c>
-      <c r="G33" s="73"/>
+      <c r="G33" s="70"/>
       <c r="H33" s="53">
         <v>46116</v>
       </c>
@@ -2667,7 +2663,7 @@
         <f t="shared" si="1"/>
         <v>25908.029999999995</v>
       </c>
-      <c r="G34" s="73"/>
+      <c r="G34" s="70"/>
       <c r="H34" s="53">
         <v>46085</v>
       </c>
@@ -2713,7 +2709,7 @@
         <f t="shared" si="1"/>
         <v>25908.029999999995</v>
       </c>
-      <c r="G35" s="73"/>
+      <c r="G35" s="70"/>
       <c r="H35" s="53">
         <v>46085</v>
       </c>
@@ -2759,7 +2755,7 @@
         <f t="shared" si="1"/>
         <v>25908.029999999995</v>
       </c>
-      <c r="G36" s="73"/>
+      <c r="G36" s="70"/>
       <c r="H36" s="53">
         <v>46087</v>
       </c>
@@ -2806,7 +2802,7 @@
         <f t="shared" si="1"/>
         <v>25908.029999999995</v>
       </c>
-      <c r="G37" s="73"/>
+      <c r="G37" s="70"/>
       <c r="H37" s="53">
         <v>46087</v>
       </c>
@@ -2846,7 +2842,7 @@
         <f t="shared" si="1"/>
         <v>25908.029999999995</v>
       </c>
-      <c r="G38" s="73"/>
+      <c r="G38" s="70"/>
       <c r="H38" s="43">
         <v>46090</v>
       </c>
@@ -2886,7 +2882,7 @@
         <f t="shared" si="1"/>
         <v>25908.029999999995</v>
       </c>
-      <c r="G39" s="73"/>
+      <c r="G39" s="70"/>
       <c r="H39" s="43">
         <v>46092</v>
       </c>
@@ -2926,7 +2922,7 @@
         <f t="shared" si="1"/>
         <v>25908.029999999995</v>
       </c>
-      <c r="G40" s="73"/>
+      <c r="G40" s="70"/>
       <c r="H40" s="43">
         <v>46092</v>
       </c>
@@ -2953,6 +2949,10 @@
         <f t="shared" si="4"/>
         <v>607</v>
       </c>
+      <c r="R40" s="2">
+        <f>R36+R10+R102</f>
+        <v>1129</v>
+      </c>
     </row>
     <row r="41" spans="2:18" ht="16" x14ac:dyDescent="0.35">
       <c r="B41" s="6"/>
@@ -2966,7 +2966,7 @@
         <f t="shared" si="1"/>
         <v>25908.029999999995</v>
       </c>
-      <c r="G41" s="73"/>
+      <c r="G41" s="70"/>
       <c r="H41" s="43">
         <v>46095</v>
       </c>
@@ -3006,7 +3006,7 @@
         <f t="shared" si="1"/>
         <v>25908.029999999995</v>
       </c>
-      <c r="G42" s="73"/>
+      <c r="G42" s="70"/>
       <c r="H42" s="43">
         <v>46095</v>
       </c>
@@ -3046,7 +3046,7 @@
         <f t="shared" si="1"/>
         <v>25908.029999999995</v>
       </c>
-      <c r="G43" s="73"/>
+      <c r="G43" s="70"/>
       <c r="H43" s="43">
         <v>46095</v>
       </c>
@@ -3086,7 +3086,7 @@
         <f t="shared" si="1"/>
         <v>25908.029999999995</v>
       </c>
-      <c r="G44" s="73"/>
+      <c r="G44" s="70"/>
       <c r="H44" s="43">
         <v>46095</v>
       </c>
@@ -3127,7 +3127,7 @@
         <f>E44</f>
         <v>25908.029999999995</v>
       </c>
-      <c r="G45" s="73"/>
+      <c r="G45" s="70"/>
       <c r="H45" s="43">
         <v>46102</v>
       </c>
@@ -3156,7 +3156,7 @@
       </c>
     </row>
     <row r="46" spans="2:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G46" s="73"/>
+      <c r="G46" s="70"/>
       <c r="H46" s="43">
         <v>46109</v>
       </c>
@@ -3185,7 +3185,7 @@
       </c>
     </row>
     <row r="47" spans="2:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G47" s="73"/>
+      <c r="G47" s="70"/>
       <c r="H47" s="24"/>
       <c r="I47" s="34"/>
       <c r="J47" s="34"/>
@@ -3204,7 +3204,7 @@
       </c>
     </row>
     <row r="48" spans="2:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G48" s="73"/>
+      <c r="G48" s="70"/>
       <c r="H48" s="24"/>
       <c r="I48" s="34"/>
       <c r="J48" s="34"/>
@@ -3223,7 +3223,7 @@
       </c>
     </row>
     <row r="49" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G49" s="73"/>
+      <c r="G49" s="70"/>
       <c r="H49" s="24"/>
       <c r="I49" s="34"/>
       <c r="J49" s="34"/>
@@ -3242,7 +3242,7 @@
       </c>
     </row>
     <row r="50" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G50" s="73"/>
+      <c r="G50" s="70"/>
       <c r="H50" s="24"/>
       <c r="I50" s="34"/>
       <c r="J50" s="34"/>
@@ -3261,7 +3261,7 @@
       </c>
     </row>
     <row r="51" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G51" s="73"/>
+      <c r="G51" s="70"/>
       <c r="H51" s="24"/>
       <c r="I51" s="34"/>
       <c r="J51" s="34"/>
@@ -3280,7 +3280,7 @@
       </c>
     </row>
     <row r="52" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G52" s="73"/>
+      <c r="G52" s="70"/>
       <c r="H52" s="24"/>
       <c r="I52" s="34"/>
       <c r="J52" s="34"/>
@@ -3299,7 +3299,7 @@
       </c>
     </row>
     <row r="53" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G53" s="73"/>
+      <c r="G53" s="70"/>
       <c r="H53" s="24"/>
       <c r="I53" s="34"/>
       <c r="J53" s="34"/>
@@ -3318,7 +3318,7 @@
       </c>
     </row>
     <row r="54" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G54" s="73"/>
+      <c r="G54" s="70"/>
       <c r="H54" s="24"/>
       <c r="I54" s="34"/>
       <c r="J54" s="34"/>
@@ -3337,7 +3337,7 @@
       </c>
     </row>
     <row r="55" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G55" s="73"/>
+      <c r="G55" s="70"/>
       <c r="H55" s="24"/>
       <c r="I55" s="34"/>
       <c r="J55" s="34"/>
@@ -3356,7 +3356,7 @@
       </c>
     </row>
     <row r="56" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G56" s="73"/>
+      <c r="G56" s="70"/>
       <c r="H56" s="24"/>
       <c r="I56" s="34"/>
       <c r="J56" s="34"/>
@@ -3375,7 +3375,7 @@
       </c>
     </row>
     <row r="57" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G57" s="73"/>
+      <c r="G57" s="70"/>
       <c r="H57" s="24"/>
       <c r="I57" s="34"/>
       <c r="J57" s="34"/>
@@ -3394,7 +3394,7 @@
       </c>
     </row>
     <row r="58" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G58" s="73"/>
+      <c r="G58" s="70"/>
       <c r="H58" s="24"/>
       <c r="I58" s="34"/>
       <c r="J58" s="34"/>
@@ -3413,7 +3413,7 @@
       </c>
     </row>
     <row r="59" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G59" s="73"/>
+      <c r="G59" s="70"/>
       <c r="H59" s="24"/>
       <c r="I59" s="34"/>
       <c r="J59" s="34"/>
@@ -3432,7 +3432,7 @@
       </c>
     </row>
     <row r="60" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G60" s="73"/>
+      <c r="G60" s="70"/>
       <c r="H60" s="24"/>
       <c r="I60" s="34"/>
       <c r="J60" s="34"/>
@@ -3451,7 +3451,7 @@
       </c>
     </row>
     <row r="61" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G61" s="73"/>
+      <c r="G61" s="70"/>
       <c r="H61" s="24"/>
       <c r="I61" s="34"/>
       <c r="J61" s="34"/>
@@ -3470,7 +3470,7 @@
       </c>
     </row>
     <row r="62" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G62" s="73"/>
+      <c r="G62" s="70"/>
       <c r="H62" s="24"/>
       <c r="I62" s="34"/>
       <c r="J62" s="34"/>
@@ -3489,7 +3489,7 @@
       </c>
     </row>
     <row r="63" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G63" s="73"/>
+      <c r="G63" s="70"/>
       <c r="H63" s="24"/>
       <c r="I63" s="34"/>
       <c r="J63" s="34"/>
@@ -3508,7 +3508,7 @@
       </c>
     </row>
     <row r="64" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G64" s="73"/>
+      <c r="G64" s="70"/>
       <c r="H64" s="24"/>
       <c r="I64" s="34"/>
       <c r="J64" s="34"/>
@@ -3527,7 +3527,7 @@
       </c>
     </row>
     <row r="65" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G65" s="73"/>
+      <c r="G65" s="70"/>
       <c r="H65" s="24"/>
       <c r="I65" s="34"/>
       <c r="J65" s="34"/>
@@ -3546,7 +3546,7 @@
       </c>
     </row>
     <row r="66" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G66" s="73"/>
+      <c r="G66" s="70"/>
       <c r="H66" s="24"/>
       <c r="I66" s="34"/>
       <c r="J66" s="34"/>
@@ -3565,7 +3565,7 @@
       </c>
     </row>
     <row r="67" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G67" s="73"/>
+      <c r="G67" s="70"/>
       <c r="H67" s="24"/>
       <c r="I67" s="34"/>
       <c r="J67" s="34"/>
@@ -3584,7 +3584,7 @@
       </c>
     </row>
     <row r="68" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G68" s="73"/>
+      <c r="G68" s="70"/>
       <c r="H68" s="24"/>
       <c r="I68" s="34"/>
       <c r="J68" s="34"/>
@@ -3603,7 +3603,7 @@
       </c>
     </row>
     <row r="69" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G69" s="73"/>
+      <c r="G69" s="70"/>
       <c r="H69" s="24"/>
       <c r="I69" s="34"/>
       <c r="J69" s="34"/>
@@ -3622,7 +3622,7 @@
       </c>
     </row>
     <row r="70" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G70" s="73"/>
+      <c r="G70" s="70"/>
       <c r="H70" s="24"/>
       <c r="I70" s="34"/>
       <c r="J70" s="34"/>
@@ -3641,7 +3641,7 @@
       </c>
     </row>
     <row r="71" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G71" s="73"/>
+      <c r="G71" s="70"/>
       <c r="H71" s="24"/>
       <c r="I71" s="34"/>
       <c r="J71" s="34"/>
@@ -3660,7 +3660,7 @@
       </c>
     </row>
     <row r="72" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G72" s="73"/>
+      <c r="G72" s="70"/>
       <c r="H72" s="24"/>
       <c r="I72" s="34"/>
       <c r="J72" s="34"/>
@@ -3679,7 +3679,7 @@
       </c>
     </row>
     <row r="73" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G73" s="73"/>
+      <c r="G73" s="70"/>
       <c r="H73" s="24"/>
       <c r="I73" s="34"/>
       <c r="J73" s="34"/>
@@ -3698,7 +3698,7 @@
       </c>
     </row>
     <row r="74" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G74" s="73"/>
+      <c r="G74" s="70"/>
       <c r="H74" s="24"/>
       <c r="I74" s="34"/>
       <c r="J74" s="34"/>
@@ -3717,7 +3717,7 @@
       </c>
     </row>
     <row r="75" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G75" s="73"/>
+      <c r="G75" s="70"/>
       <c r="H75" s="24"/>
       <c r="I75" s="34"/>
       <c r="J75" s="34"/>
@@ -3736,7 +3736,7 @@
       </c>
     </row>
     <row r="76" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G76" s="73"/>
+      <c r="G76" s="70"/>
       <c r="H76" s="24"/>
       <c r="I76" s="34"/>
       <c r="J76" s="34"/>
@@ -3755,7 +3755,7 @@
       </c>
     </row>
     <row r="77" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G77" s="73"/>
+      <c r="G77" s="70"/>
       <c r="H77" s="24"/>
       <c r="I77" s="34"/>
       <c r="J77" s="34"/>
@@ -3774,7 +3774,7 @@
       </c>
     </row>
     <row r="78" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G78" s="73"/>
+      <c r="G78" s="70"/>
       <c r="H78" s="24"/>
       <c r="I78" s="34"/>
       <c r="J78" s="34"/>
@@ -3793,7 +3793,7 @@
       </c>
     </row>
     <row r="79" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G79" s="73"/>
+      <c r="G79" s="70"/>
       <c r="H79" s="24"/>
       <c r="I79" s="34"/>
       <c r="J79" s="34"/>
@@ -3812,7 +3812,7 @@
       </c>
     </row>
     <row r="80" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G80" s="73"/>
+      <c r="G80" s="70"/>
       <c r="H80" s="24"/>
       <c r="I80" s="34"/>
       <c r="J80" s="34"/>
@@ -3831,7 +3831,7 @@
       </c>
     </row>
     <row r="81" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G81" s="73"/>
+      <c r="G81" s="70"/>
       <c r="H81" s="24"/>
       <c r="I81" s="34"/>
       <c r="J81" s="34"/>
@@ -3850,7 +3850,7 @@
       </c>
     </row>
     <row r="82" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G82" s="73"/>
+      <c r="G82" s="70"/>
       <c r="H82" s="24"/>
       <c r="I82" s="34"/>
       <c r="J82" s="34"/>
@@ -3869,7 +3869,7 @@
       </c>
     </row>
     <row r="83" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G83" s="73"/>
+      <c r="G83" s="70"/>
       <c r="H83" s="24"/>
       <c r="I83" s="34"/>
       <c r="J83" s="34"/>
@@ -3888,7 +3888,7 @@
       </c>
     </row>
     <row r="84" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G84" s="73"/>
+      <c r="G84" s="70"/>
       <c r="H84" s="24"/>
       <c r="I84" s="34"/>
       <c r="J84" s="34"/>
@@ -3907,7 +3907,7 @@
       </c>
     </row>
     <row r="85" spans="7:15" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G85" s="74"/>
+      <c r="G85" s="71"/>
       <c r="H85" s="36"/>
       <c r="I85" s="37"/>
       <c r="J85" s="37"/>
@@ -3946,19 +3946,19 @@
     </row>
     <row r="88" spans="7:15" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="89" spans="7:15" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="H89" s="69" t="s">
+      <c r="H89" s="72" t="s">
         <v>45</v>
       </c>
-      <c r="I89" s="70"/>
-      <c r="J89" s="70"/>
-      <c r="K89" s="70"/>
-      <c r="L89" s="70"/>
-      <c r="M89" s="70"/>
-      <c r="N89" s="70"/>
-      <c r="O89" s="71"/>
+      <c r="I89" s="73"/>
+      <c r="J89" s="73"/>
+      <c r="K89" s="73"/>
+      <c r="L89" s="73"/>
+      <c r="M89" s="73"/>
+      <c r="N89" s="73"/>
+      <c r="O89" s="74"/>
     </row>
     <row r="90" spans="7:15" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G90" s="80" t="s">
+      <c r="G90" s="78" t="s">
         <v>33</v>
       </c>
       <c r="H90" s="56" t="s">
@@ -3987,7 +3987,7 @@
       </c>
     </row>
     <row r="91" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G91" s="73"/>
+      <c r="G91" s="70"/>
       <c r="H91" s="30"/>
       <c r="I91" s="31">
         <v>10</v>
@@ -4014,7 +4014,7 @@
       </c>
     </row>
     <row r="92" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G92" s="73"/>
+      <c r="G92" s="70"/>
       <c r="H92" s="24"/>
       <c r="I92" s="34">
         <v>10</v>
@@ -4029,7 +4029,7 @@
         <v>35</v>
       </c>
       <c r="M92" s="22">
-        <f t="shared" ref="M92:M128" si="5">K92*I92</f>
+        <f t="shared" ref="M92:M127" si="5">K92*I92</f>
         <v>35</v>
       </c>
       <c r="N92" s="22">
@@ -4041,7 +4041,7 @@
       </c>
     </row>
     <row r="93" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G93" s="73"/>
+      <c r="G93" s="70"/>
       <c r="H93" s="24"/>
       <c r="I93" s="34">
         <v>10</v>
@@ -4068,7 +4068,7 @@
       </c>
     </row>
     <row r="94" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G94" s="73"/>
+      <c r="G94" s="70"/>
       <c r="H94" s="24"/>
       <c r="I94" s="34">
         <v>5</v>
@@ -4095,7 +4095,7 @@
       </c>
     </row>
     <row r="95" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G95" s="73"/>
+      <c r="G95" s="70"/>
       <c r="H95" s="24"/>
       <c r="I95" s="34">
         <v>5</v>
@@ -4122,7 +4122,7 @@
       </c>
     </row>
     <row r="96" spans="7:15" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G96" s="73"/>
+      <c r="G96" s="70"/>
       <c r="H96" s="24"/>
       <c r="I96" s="34">
         <v>10</v>
@@ -4149,7 +4149,7 @@
       </c>
     </row>
     <row r="97" spans="7:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G97" s="73"/>
+      <c r="G97" s="70"/>
       <c r="H97" s="24"/>
       <c r="I97" s="34">
         <v>7</v>
@@ -4174,13 +4174,13 @@
         <f t="shared" si="6"/>
         <v>1099</v>
       </c>
-      <c r="Q97" s="75" t="s">
+      <c r="Q97" s="79" t="s">
         <v>64</v>
       </c>
-      <c r="R97" s="76"/>
+      <c r="R97" s="80"/>
     </row>
     <row r="98" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G98" s="73"/>
+      <c r="G98" s="70"/>
       <c r="H98" s="24"/>
       <c r="I98" s="34">
         <v>6</v>
@@ -4202,7 +4202,7 @@
         <v>0</v>
       </c>
       <c r="O98" s="35">
-        <f t="shared" si="6"/>
+        <f>O97+M98-N98</f>
         <v>1129</v>
       </c>
       <c r="Q98" s="61" t="s">
@@ -4211,7 +4211,7 @@
       <c r="R98" s="62"/>
     </row>
     <row r="99" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G99" s="73"/>
+      <c r="G99" s="70"/>
       <c r="H99" s="24"/>
       <c r="I99" s="34"/>
       <c r="J99" s="34"/>
@@ -4234,7 +4234,7 @@
       <c r="R99" s="64"/>
     </row>
     <row r="100" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G100" s="73"/>
+      <c r="G100" s="70"/>
       <c r="H100" s="24"/>
       <c r="I100" s="34"/>
       <c r="J100" s="34"/>
@@ -4257,7 +4257,7 @@
       <c r="R100" s="64"/>
     </row>
     <row r="101" spans="7:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G101" s="73"/>
+      <c r="G101" s="70"/>
       <c r="H101" s="24"/>
       <c r="I101" s="34"/>
       <c r="J101" s="34"/>
@@ -4280,7 +4280,7 @@
       <c r="R101" s="66"/>
     </row>
     <row r="102" spans="7:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G102" s="73"/>
+      <c r="G102" s="70"/>
       <c r="H102" s="24"/>
       <c r="I102" s="34"/>
       <c r="J102" s="34"/>
@@ -4306,7 +4306,7 @@
       </c>
     </row>
     <row r="103" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G103" s="73"/>
+      <c r="G103" s="70"/>
       <c r="H103" s="24"/>
       <c r="I103" s="34"/>
       <c r="J103" s="34"/>
@@ -4325,7 +4325,7 @@
       </c>
     </row>
     <row r="104" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G104" s="73"/>
+      <c r="G104" s="70"/>
       <c r="H104" s="24"/>
       <c r="I104" s="34"/>
       <c r="J104" s="34"/>
@@ -4344,7 +4344,7 @@
       </c>
     </row>
     <row r="105" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G105" s="73"/>
+      <c r="G105" s="70"/>
       <c r="H105" s="24"/>
       <c r="I105" s="34"/>
       <c r="J105" s="34"/>
@@ -4363,7 +4363,7 @@
       </c>
     </row>
     <row r="106" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G106" s="73"/>
+      <c r="G106" s="70"/>
       <c r="H106" s="24"/>
       <c r="I106" s="34"/>
       <c r="J106" s="34"/>
@@ -4382,7 +4382,7 @@
       </c>
     </row>
     <row r="107" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G107" s="73"/>
+      <c r="G107" s="70"/>
       <c r="H107" s="24"/>
       <c r="I107" s="34"/>
       <c r="J107" s="34"/>
@@ -4401,7 +4401,7 @@
       </c>
     </row>
     <row r="108" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G108" s="73"/>
+      <c r="G108" s="70"/>
       <c r="H108" s="24"/>
       <c r="I108" s="34"/>
       <c r="J108" s="34"/>
@@ -4420,7 +4420,7 @@
       </c>
     </row>
     <row r="109" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G109" s="73"/>
+      <c r="G109" s="70"/>
       <c r="H109" s="24"/>
       <c r="I109" s="34"/>
       <c r="J109" s="34"/>
@@ -4439,7 +4439,7 @@
       </c>
     </row>
     <row r="110" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G110" s="73"/>
+      <c r="G110" s="70"/>
       <c r="H110" s="24"/>
       <c r="I110" s="34"/>
       <c r="J110" s="34"/>
@@ -4458,7 +4458,7 @@
       </c>
     </row>
     <row r="111" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G111" s="73"/>
+      <c r="G111" s="70"/>
       <c r="H111" s="24"/>
       <c r="I111" s="34"/>
       <c r="J111" s="34"/>
@@ -4477,7 +4477,7 @@
       </c>
     </row>
     <row r="112" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G112" s="73"/>
+      <c r="G112" s="70"/>
       <c r="H112" s="24"/>
       <c r="I112" s="34"/>
       <c r="J112" s="34"/>
@@ -4496,7 +4496,7 @@
       </c>
     </row>
     <row r="113" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G113" s="73"/>
+      <c r="G113" s="70"/>
       <c r="H113" s="24"/>
       <c r="I113" s="34"/>
       <c r="J113" s="34"/>
@@ -4515,7 +4515,7 @@
       </c>
     </row>
     <row r="114" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G114" s="73"/>
+      <c r="G114" s="70"/>
       <c r="H114" s="24"/>
       <c r="I114" s="34"/>
       <c r="J114" s="34"/>
@@ -4534,7 +4534,7 @@
       </c>
     </row>
     <row r="115" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G115" s="73"/>
+      <c r="G115" s="70"/>
       <c r="H115" s="24"/>
       <c r="I115" s="34"/>
       <c r="J115" s="34"/>
@@ -4553,7 +4553,7 @@
       </c>
     </row>
     <row r="116" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G116" s="73"/>
+      <c r="G116" s="70"/>
       <c r="H116" s="24"/>
       <c r="I116" s="34"/>
       <c r="J116" s="34"/>
@@ -4572,7 +4572,7 @@
       </c>
     </row>
     <row r="117" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G117" s="73"/>
+      <c r="G117" s="70"/>
       <c r="H117" s="24"/>
       <c r="I117" s="34"/>
       <c r="J117" s="34"/>
@@ -4591,7 +4591,7 @@
       </c>
     </row>
     <row r="118" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G118" s="73"/>
+      <c r="G118" s="70"/>
       <c r="H118" s="24"/>
       <c r="I118" s="34"/>
       <c r="J118" s="34"/>
@@ -4610,7 +4610,7 @@
       </c>
     </row>
     <row r="119" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G119" s="73"/>
+      <c r="G119" s="70"/>
       <c r="H119" s="24"/>
       <c r="I119" s="34"/>
       <c r="J119" s="34"/>
@@ -4629,7 +4629,7 @@
       </c>
     </row>
     <row r="120" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G120" s="73"/>
+      <c r="G120" s="70"/>
       <c r="H120" s="24"/>
       <c r="I120" s="34"/>
       <c r="J120" s="34"/>
@@ -4648,7 +4648,7 @@
       </c>
     </row>
     <row r="121" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G121" s="73"/>
+      <c r="G121" s="70"/>
       <c r="H121" s="24"/>
       <c r="I121" s="34"/>
       <c r="J121" s="34"/>
@@ -4667,7 +4667,7 @@
       </c>
     </row>
     <row r="122" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G122" s="73"/>
+      <c r="G122" s="70"/>
       <c r="H122" s="24"/>
       <c r="I122" s="34"/>
       <c r="J122" s="34"/>
@@ -4686,7 +4686,7 @@
       </c>
     </row>
     <row r="123" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G123" s="73"/>
+      <c r="G123" s="70"/>
       <c r="H123" s="24"/>
       <c r="I123" s="34"/>
       <c r="J123" s="34"/>
@@ -4705,7 +4705,7 @@
       </c>
     </row>
     <row r="124" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G124" s="73"/>
+      <c r="G124" s="70"/>
       <c r="H124" s="24"/>
       <c r="I124" s="34"/>
       <c r="J124" s="34"/>
@@ -4724,7 +4724,7 @@
       </c>
     </row>
     <row r="125" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G125" s="73"/>
+      <c r="G125" s="70"/>
       <c r="H125" s="24"/>
       <c r="I125" s="34"/>
       <c r="J125" s="34"/>
@@ -4743,7 +4743,7 @@
       </c>
     </row>
     <row r="126" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G126" s="73"/>
+      <c r="G126" s="70"/>
       <c r="H126" s="24"/>
       <c r="I126" s="34"/>
       <c r="J126" s="34"/>
@@ -4762,7 +4762,7 @@
       </c>
     </row>
     <row r="127" spans="7:15" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G127" s="74"/>
+      <c r="G127" s="71"/>
       <c r="H127" s="36"/>
       <c r="I127" s="37"/>
       <c r="J127" s="37"/>
@@ -4794,7 +4794,7 @@
         <v>0</v>
       </c>
       <c r="O128" s="49">
-        <f t="shared" si="7"/>
+        <f>O127+M128-N128</f>
         <v>1423</v>
       </c>
     </row>
@@ -4802,21 +4802,24 @@
       <c r="M129" s="2"/>
       <c r="N129" s="2"/>
     </row>
+    <row r="130" spans="7:18" x14ac:dyDescent="0.35">
+      <c r="M130" s="2"/>
+    </row>
     <row r="132" spans="7:18" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="133" spans="7:18" ht="31" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="H133" s="69" t="s">
+      <c r="H133" s="72" t="s">
         <v>46</v>
       </c>
-      <c r="I133" s="70"/>
-      <c r="J133" s="70"/>
-      <c r="K133" s="70"/>
-      <c r="L133" s="70"/>
-      <c r="M133" s="70"/>
-      <c r="N133" s="70"/>
-      <c r="O133" s="71"/>
+      <c r="I133" s="73"/>
+      <c r="J133" s="73"/>
+      <c r="K133" s="73"/>
+      <c r="L133" s="73"/>
+      <c r="M133" s="73"/>
+      <c r="N133" s="73"/>
+      <c r="O133" s="74"/>
     </row>
     <row r="134" spans="7:18" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="G134" s="72" t="s">
+      <c r="G134" s="69" t="s">
         <v>42</v>
       </c>
       <c r="H134" s="56" t="s">
@@ -4845,7 +4848,7 @@
       </c>
     </row>
     <row r="135" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G135" s="73"/>
+      <c r="G135" s="70"/>
       <c r="H135" s="53"/>
       <c r="I135" s="54"/>
       <c r="J135" s="54"/>
@@ -4864,7 +4867,7 @@
       </c>
     </row>
     <row r="136" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G136" s="73"/>
+      <c r="G136" s="70"/>
       <c r="H136" s="53"/>
       <c r="I136" s="34"/>
       <c r="J136" s="34"/>
@@ -4883,7 +4886,7 @@
       </c>
     </row>
     <row r="137" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G137" s="73"/>
+      <c r="G137" s="70"/>
       <c r="H137" s="53"/>
       <c r="I137" s="34"/>
       <c r="J137" s="34"/>
@@ -4902,7 +4905,7 @@
       </c>
     </row>
     <row r="138" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G138" s="73"/>
+      <c r="G138" s="70"/>
       <c r="H138" s="53"/>
       <c r="I138" s="34"/>
       <c r="J138" s="34"/>
@@ -4921,7 +4924,7 @@
       </c>
     </row>
     <row r="139" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G139" s="73"/>
+      <c r="G139" s="70"/>
       <c r="H139" s="53"/>
       <c r="I139" s="34"/>
       <c r="J139" s="34"/>
@@ -4940,7 +4943,7 @@
       </c>
     </row>
     <row r="140" spans="7:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G140" s="73"/>
+      <c r="G140" s="70"/>
       <c r="H140" s="53"/>
       <c r="I140" s="34"/>
       <c r="J140" s="34"/>
@@ -4959,7 +4962,7 @@
       </c>
     </row>
     <row r="141" spans="7:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G141" s="73"/>
+      <c r="G141" s="70"/>
       <c r="H141" s="53"/>
       <c r="I141" s="34"/>
       <c r="J141" s="34"/>
@@ -4976,13 +4979,13 @@
         <f t="shared" si="9"/>
         <v>1423</v>
       </c>
-      <c r="Q141" s="75" t="s">
+      <c r="Q141" s="79" t="s">
         <v>65</v>
       </c>
-      <c r="R141" s="76"/>
+      <c r="R141" s="80"/>
     </row>
     <row r="142" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G142" s="73"/>
+      <c r="G142" s="70"/>
       <c r="H142" s="53"/>
       <c r="I142" s="34"/>
       <c r="J142" s="34"/>
@@ -5005,7 +5008,7 @@
       <c r="R142" s="62"/>
     </row>
     <row r="143" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G143" s="73"/>
+      <c r="G143" s="70"/>
       <c r="H143" s="43"/>
       <c r="I143" s="34"/>
       <c r="J143" s="34"/>
@@ -5028,7 +5031,7 @@
       <c r="R143" s="64"/>
     </row>
     <row r="144" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G144" s="73"/>
+      <c r="G144" s="70"/>
       <c r="H144" s="43"/>
       <c r="I144" s="34"/>
       <c r="J144" s="34"/>
@@ -5051,7 +5054,7 @@
       <c r="R144" s="64"/>
     </row>
     <row r="145" spans="7:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G145" s="73"/>
+      <c r="G145" s="70"/>
       <c r="H145" s="43"/>
       <c r="I145" s="34"/>
       <c r="J145" s="34"/>
@@ -5074,7 +5077,7 @@
       <c r="R145" s="66"/>
     </row>
     <row r="146" spans="7:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G146" s="73"/>
+      <c r="G146" s="70"/>
       <c r="H146" s="43"/>
       <c r="I146" s="34"/>
       <c r="J146" s="34"/>
@@ -5100,7 +5103,7 @@
       </c>
     </row>
     <row r="147" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G147" s="73"/>
+      <c r="G147" s="70"/>
       <c r="H147" s="43"/>
       <c r="I147" s="34"/>
       <c r="J147" s="34"/>
@@ -5119,7 +5122,7 @@
       </c>
     </row>
     <row r="148" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G148" s="73"/>
+      <c r="G148" s="70"/>
       <c r="H148" s="43"/>
       <c r="I148" s="34"/>
       <c r="J148" s="34"/>
@@ -5138,7 +5141,7 @@
       </c>
     </row>
     <row r="149" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G149" s="73"/>
+      <c r="G149" s="70"/>
       <c r="H149" s="43"/>
       <c r="I149" s="34"/>
       <c r="J149" s="34"/>
@@ -5157,7 +5160,7 @@
       </c>
     </row>
     <row r="150" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G150" s="73"/>
+      <c r="G150" s="70"/>
       <c r="H150" s="43"/>
       <c r="I150" s="34"/>
       <c r="J150" s="34"/>
@@ -5176,7 +5179,7 @@
       </c>
     </row>
     <row r="151" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G151" s="73"/>
+      <c r="G151" s="70"/>
       <c r="H151" s="43"/>
       <c r="I151" s="34"/>
       <c r="J151" s="34"/>
@@ -5195,7 +5198,7 @@
       </c>
     </row>
     <row r="152" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G152" s="73"/>
+      <c r="G152" s="70"/>
       <c r="H152" s="24"/>
       <c r="I152" s="34"/>
       <c r="J152" s="34"/>
@@ -5214,7 +5217,7 @@
       </c>
     </row>
     <row r="153" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G153" s="73"/>
+      <c r="G153" s="70"/>
       <c r="H153" s="24"/>
       <c r="I153" s="34"/>
       <c r="J153" s="34"/>
@@ -5233,7 +5236,7 @@
       </c>
     </row>
     <row r="154" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G154" s="73"/>
+      <c r="G154" s="70"/>
       <c r="H154" s="24"/>
       <c r="I154" s="34"/>
       <c r="J154" s="34"/>
@@ -5252,7 +5255,7 @@
       </c>
     </row>
     <row r="155" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G155" s="73"/>
+      <c r="G155" s="70"/>
       <c r="H155" s="24"/>
       <c r="I155" s="34"/>
       <c r="J155" s="34"/>
@@ -5271,7 +5274,7 @@
       </c>
     </row>
     <row r="156" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G156" s="73"/>
+      <c r="G156" s="70"/>
       <c r="H156" s="24"/>
       <c r="I156" s="34"/>
       <c r="J156" s="34"/>
@@ -5290,7 +5293,7 @@
       </c>
     </row>
     <row r="157" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G157" s="73"/>
+      <c r="G157" s="70"/>
       <c r="H157" s="24"/>
       <c r="I157" s="34"/>
       <c r="J157" s="34"/>
@@ -5309,7 +5312,7 @@
       </c>
     </row>
     <row r="158" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G158" s="73"/>
+      <c r="G158" s="70"/>
       <c r="H158" s="24"/>
       <c r="I158" s="34"/>
       <c r="J158" s="34"/>
@@ -5328,7 +5331,7 @@
       </c>
     </row>
     <row r="159" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G159" s="73"/>
+      <c r="G159" s="70"/>
       <c r="H159" s="24"/>
       <c r="I159" s="34"/>
       <c r="J159" s="34"/>
@@ -5347,7 +5350,7 @@
       </c>
     </row>
     <row r="160" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G160" s="73"/>
+      <c r="G160" s="70"/>
       <c r="H160" s="24"/>
       <c r="I160" s="34"/>
       <c r="J160" s="34"/>
@@ -5366,7 +5369,7 @@
       </c>
     </row>
     <row r="161" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G161" s="73"/>
+      <c r="G161" s="70"/>
       <c r="H161" s="24"/>
       <c r="I161" s="34"/>
       <c r="J161" s="34"/>
@@ -5385,7 +5388,7 @@
       </c>
     </row>
     <row r="162" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G162" s="73"/>
+      <c r="G162" s="70"/>
       <c r="H162" s="24"/>
       <c r="I162" s="34"/>
       <c r="J162" s="34"/>
@@ -5404,7 +5407,7 @@
       </c>
     </row>
     <row r="163" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G163" s="73"/>
+      <c r="G163" s="70"/>
       <c r="H163" s="24"/>
       <c r="I163" s="34"/>
       <c r="J163" s="34"/>
@@ -5423,7 +5426,7 @@
       </c>
     </row>
     <row r="164" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G164" s="73"/>
+      <c r="G164" s="70"/>
       <c r="H164" s="24"/>
       <c r="I164" s="34"/>
       <c r="J164" s="34"/>
@@ -5442,7 +5445,7 @@
       </c>
     </row>
     <row r="165" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G165" s="73"/>
+      <c r="G165" s="70"/>
       <c r="H165" s="24"/>
       <c r="I165" s="34"/>
       <c r="J165" s="34"/>
@@ -5461,7 +5464,7 @@
       </c>
     </row>
     <row r="166" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G166" s="73"/>
+      <c r="G166" s="70"/>
       <c r="H166" s="24"/>
       <c r="I166" s="34"/>
       <c r="J166" s="34"/>
@@ -5480,7 +5483,7 @@
       </c>
     </row>
     <row r="167" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G167" s="73"/>
+      <c r="G167" s="70"/>
       <c r="H167" s="24"/>
       <c r="I167" s="34"/>
       <c r="J167" s="34"/>
@@ -5499,7 +5502,7 @@
       </c>
     </row>
     <row r="168" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G168" s="73"/>
+      <c r="G168" s="70"/>
       <c r="H168" s="24"/>
       <c r="I168" s="34"/>
       <c r="J168" s="34"/>
@@ -5518,7 +5521,7 @@
       </c>
     </row>
     <row r="169" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G169" s="73"/>
+      <c r="G169" s="70"/>
       <c r="H169" s="24"/>
       <c r="I169" s="34"/>
       <c r="J169" s="34"/>
@@ -5537,7 +5540,7 @@
       </c>
     </row>
     <row r="170" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G170" s="73"/>
+      <c r="G170" s="70"/>
       <c r="H170" s="24"/>
       <c r="I170" s="34"/>
       <c r="J170" s="34"/>
@@ -5556,7 +5559,7 @@
       </c>
     </row>
     <row r="171" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G171" s="73"/>
+      <c r="G171" s="70"/>
       <c r="H171" s="24"/>
       <c r="I171" s="34"/>
       <c r="J171" s="34"/>
@@ -5575,7 +5578,7 @@
       </c>
     </row>
     <row r="172" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G172" s="73"/>
+      <c r="G172" s="70"/>
       <c r="H172" s="24"/>
       <c r="I172" s="34"/>
       <c r="J172" s="34"/>
@@ -5594,7 +5597,7 @@
       </c>
     </row>
     <row r="173" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G173" s="73"/>
+      <c r="G173" s="70"/>
       <c r="H173" s="24"/>
       <c r="I173" s="34"/>
       <c r="J173" s="34"/>
@@ -5613,7 +5616,7 @@
       </c>
     </row>
     <row r="174" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G174" s="73"/>
+      <c r="G174" s="70"/>
       <c r="H174" s="24"/>
       <c r="I174" s="34"/>
       <c r="J174" s="34"/>
@@ -5632,7 +5635,7 @@
       </c>
     </row>
     <row r="175" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G175" s="73"/>
+      <c r="G175" s="70"/>
       <c r="H175" s="24"/>
       <c r="I175" s="34"/>
       <c r="J175" s="34"/>
@@ -5651,7 +5654,7 @@
       </c>
     </row>
     <row r="176" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G176" s="73"/>
+      <c r="G176" s="70"/>
       <c r="H176" s="24"/>
       <c r="I176" s="34"/>
       <c r="J176" s="34"/>
@@ -5670,7 +5673,7 @@
       </c>
     </row>
     <row r="177" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G177" s="73"/>
+      <c r="G177" s="70"/>
       <c r="H177" s="24"/>
       <c r="I177" s="34"/>
       <c r="J177" s="34"/>
@@ -5689,7 +5692,7 @@
       </c>
     </row>
     <row r="178" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G178" s="73"/>
+      <c r="G178" s="70"/>
       <c r="H178" s="24"/>
       <c r="I178" s="34"/>
       <c r="J178" s="34"/>
@@ -5708,7 +5711,7 @@
       </c>
     </row>
     <row r="179" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G179" s="73"/>
+      <c r="G179" s="70"/>
       <c r="H179" s="24"/>
       <c r="I179" s="34"/>
       <c r="J179" s="34"/>
@@ -5727,7 +5730,7 @@
       </c>
     </row>
     <row r="180" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G180" s="73"/>
+      <c r="G180" s="70"/>
       <c r="H180" s="24"/>
       <c r="I180" s="34"/>
       <c r="J180" s="34"/>
@@ -5746,7 +5749,7 @@
       </c>
     </row>
     <row r="181" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G181" s="73"/>
+      <c r="G181" s="70"/>
       <c r="H181" s="24"/>
       <c r="I181" s="34"/>
       <c r="J181" s="34"/>
@@ -5765,7 +5768,7 @@
       </c>
     </row>
     <row r="182" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G182" s="73"/>
+      <c r="G182" s="70"/>
       <c r="H182" s="24"/>
       <c r="I182" s="34"/>
       <c r="J182" s="34"/>
@@ -5784,7 +5787,7 @@
       </c>
     </row>
     <row r="183" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G183" s="73"/>
+      <c r="G183" s="70"/>
       <c r="H183" s="24"/>
       <c r="I183" s="34"/>
       <c r="J183" s="34"/>
@@ -5803,7 +5806,7 @@
       </c>
     </row>
     <row r="184" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G184" s="73"/>
+      <c r="G184" s="70"/>
       <c r="H184" s="24"/>
       <c r="I184" s="34"/>
       <c r="J184" s="34"/>
@@ -5822,7 +5825,7 @@
       </c>
     </row>
     <row r="185" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G185" s="73"/>
+      <c r="G185" s="70"/>
       <c r="H185" s="24"/>
       <c r="I185" s="34"/>
       <c r="J185" s="34"/>
@@ -5841,7 +5844,7 @@
       </c>
     </row>
     <row r="186" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G186" s="73"/>
+      <c r="G186" s="70"/>
       <c r="H186" s="24"/>
       <c r="I186" s="34"/>
       <c r="J186" s="34"/>
@@ -5860,7 +5863,7 @@
       </c>
     </row>
     <row r="187" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G187" s="73"/>
+      <c r="G187" s="70"/>
       <c r="H187" s="24"/>
       <c r="I187" s="34"/>
       <c r="J187" s="34"/>
@@ -5879,7 +5882,7 @@
       </c>
     </row>
     <row r="188" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G188" s="73"/>
+      <c r="G188" s="70"/>
       <c r="H188" s="24"/>
       <c r="I188" s="34"/>
       <c r="J188" s="34"/>
@@ -5898,7 +5901,7 @@
       </c>
     </row>
     <row r="189" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G189" s="73"/>
+      <c r="G189" s="70"/>
       <c r="H189" s="24"/>
       <c r="I189" s="34"/>
       <c r="J189" s="34"/>
@@ -5917,7 +5920,7 @@
       </c>
     </row>
     <row r="190" spans="7:15" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G190" s="74"/>
+      <c r="G190" s="71"/>
       <c r="H190" s="36"/>
       <c r="I190" s="37"/>
       <c r="J190" s="37"/>
@@ -5956,19 +5959,19 @@
     </row>
     <row r="194" spans="7:15" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="195" spans="7:15" ht="31" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="H195" s="69" t="s">
+      <c r="H195" s="72" t="s">
         <v>47</v>
       </c>
-      <c r="I195" s="70"/>
-      <c r="J195" s="70"/>
-      <c r="K195" s="70"/>
-      <c r="L195" s="70"/>
-      <c r="M195" s="70"/>
-      <c r="N195" s="70"/>
-      <c r="O195" s="71"/>
+      <c r="I195" s="73"/>
+      <c r="J195" s="73"/>
+      <c r="K195" s="73"/>
+      <c r="L195" s="73"/>
+      <c r="M195" s="73"/>
+      <c r="N195" s="73"/>
+      <c r="O195" s="74"/>
     </row>
     <row r="196" spans="7:15" ht="27" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="G196" s="72" t="s">
+      <c r="G196" s="69" t="s">
         <v>48</v>
       </c>
       <c r="H196" s="56" t="s">
@@ -5997,7 +6000,7 @@
       </c>
     </row>
     <row r="197" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G197" s="73"/>
+      <c r="G197" s="70"/>
       <c r="H197" s="53"/>
       <c r="I197" s="54"/>
       <c r="J197" s="54"/>
@@ -6016,7 +6019,7 @@
       </c>
     </row>
     <row r="198" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G198" s="73"/>
+      <c r="G198" s="70"/>
       <c r="H198" s="53"/>
       <c r="I198" s="34"/>
       <c r="J198" s="34"/>
@@ -6035,7 +6038,7 @@
       </c>
     </row>
     <row r="199" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G199" s="73"/>
+      <c r="G199" s="70"/>
       <c r="H199" s="53"/>
       <c r="I199" s="34"/>
       <c r="J199" s="34"/>
@@ -6054,7 +6057,7 @@
       </c>
     </row>
     <row r="200" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G200" s="73"/>
+      <c r="G200" s="70"/>
       <c r="H200" s="53"/>
       <c r="I200" s="34"/>
       <c r="J200" s="34"/>
@@ -6073,7 +6076,7 @@
       </c>
     </row>
     <row r="201" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G201" s="73"/>
+      <c r="G201" s="70"/>
       <c r="H201" s="53"/>
       <c r="I201" s="34"/>
       <c r="J201" s="34"/>
@@ -6092,7 +6095,7 @@
       </c>
     </row>
     <row r="202" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G202" s="73"/>
+      <c r="G202" s="70"/>
       <c r="H202" s="53"/>
       <c r="I202" s="34"/>
       <c r="J202" s="34"/>
@@ -6111,7 +6114,7 @@
       </c>
     </row>
     <row r="203" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G203" s="73"/>
+      <c r="G203" s="70"/>
       <c r="H203" s="53"/>
       <c r="I203" s="34"/>
       <c r="J203" s="34"/>
@@ -6130,7 +6133,7 @@
       </c>
     </row>
     <row r="204" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G204" s="73"/>
+      <c r="G204" s="70"/>
       <c r="H204" s="53"/>
       <c r="I204" s="34"/>
       <c r="J204" s="34"/>
@@ -6149,7 +6152,7 @@
       </c>
     </row>
     <row r="205" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G205" s="73"/>
+      <c r="G205" s="70"/>
       <c r="H205" s="43"/>
       <c r="I205" s="34"/>
       <c r="J205" s="34"/>
@@ -6168,7 +6171,7 @@
       </c>
     </row>
     <row r="206" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G206" s="73"/>
+      <c r="G206" s="70"/>
       <c r="H206" s="43"/>
       <c r="I206" s="34"/>
       <c r="J206" s="34"/>
@@ -6187,7 +6190,7 @@
       </c>
     </row>
     <row r="207" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G207" s="73"/>
+      <c r="G207" s="70"/>
       <c r="H207" s="43"/>
       <c r="I207" s="34"/>
       <c r="J207" s="34"/>
@@ -6206,7 +6209,7 @@
       </c>
     </row>
     <row r="208" spans="7:15" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G208" s="73"/>
+      <c r="G208" s="70"/>
       <c r="H208" s="43"/>
       <c r="I208" s="34"/>
       <c r="J208" s="34"/>
@@ -6225,7 +6228,7 @@
       </c>
     </row>
     <row r="209" spans="7:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G209" s="73"/>
+      <c r="G209" s="70"/>
       <c r="H209" s="43"/>
       <c r="I209" s="34"/>
       <c r="J209" s="34"/>
@@ -6242,13 +6245,13 @@
         <f t="shared" si="11"/>
         <v>1423</v>
       </c>
-      <c r="Q209" s="75" t="s">
+      <c r="Q209" s="79" t="s">
         <v>66</v>
       </c>
-      <c r="R209" s="76"/>
+      <c r="R209" s="80"/>
     </row>
     <row r="210" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G210" s="73"/>
+      <c r="G210" s="70"/>
       <c r="H210" s="43"/>
       <c r="I210" s="34"/>
       <c r="J210" s="34"/>
@@ -6271,7 +6274,7 @@
       <c r="R210" s="62"/>
     </row>
     <row r="211" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G211" s="73"/>
+      <c r="G211" s="70"/>
       <c r="H211" s="43"/>
       <c r="I211" s="34"/>
       <c r="J211" s="34"/>
@@ -6294,7 +6297,7 @@
       <c r="R211" s="64"/>
     </row>
     <row r="212" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G212" s="73"/>
+      <c r="G212" s="70"/>
       <c r="H212" s="43"/>
       <c r="I212" s="34"/>
       <c r="J212" s="34"/>
@@ -6317,7 +6320,7 @@
       <c r="R212" s="64"/>
     </row>
     <row r="213" spans="7:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G213" s="73"/>
+      <c r="G213" s="70"/>
       <c r="H213" s="43"/>
       <c r="I213" s="34"/>
       <c r="J213" s="34"/>
@@ -6340,7 +6343,7 @@
       <c r="R213" s="66"/>
     </row>
     <row r="214" spans="7:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G214" s="73"/>
+      <c r="G214" s="70"/>
       <c r="H214" s="24"/>
       <c r="I214" s="34"/>
       <c r="J214" s="34"/>
@@ -6366,7 +6369,7 @@
       </c>
     </row>
     <row r="215" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G215" s="73"/>
+      <c r="G215" s="70"/>
       <c r="H215" s="24"/>
       <c r="I215" s="34"/>
       <c r="J215" s="34"/>
@@ -6385,7 +6388,7 @@
       </c>
     </row>
     <row r="216" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G216" s="73"/>
+      <c r="G216" s="70"/>
       <c r="H216" s="24"/>
       <c r="I216" s="34"/>
       <c r="J216" s="34"/>
@@ -6404,7 +6407,7 @@
       </c>
     </row>
     <row r="217" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G217" s="73"/>
+      <c r="G217" s="70"/>
       <c r="H217" s="24"/>
       <c r="I217" s="34"/>
       <c r="J217" s="34"/>
@@ -6423,7 +6426,7 @@
       </c>
     </row>
     <row r="218" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G218" s="73"/>
+      <c r="G218" s="70"/>
       <c r="H218" s="24"/>
       <c r="I218" s="34"/>
       <c r="J218" s="34"/>
@@ -6442,7 +6445,7 @@
       </c>
     </row>
     <row r="219" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G219" s="73"/>
+      <c r="G219" s="70"/>
       <c r="H219" s="24"/>
       <c r="I219" s="34"/>
       <c r="J219" s="34"/>
@@ -6461,7 +6464,7 @@
       </c>
     </row>
     <row r="220" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G220" s="73"/>
+      <c r="G220" s="70"/>
       <c r="H220" s="24"/>
       <c r="I220" s="34"/>
       <c r="J220" s="34"/>
@@ -6480,7 +6483,7 @@
       </c>
     </row>
     <row r="221" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G221" s="73"/>
+      <c r="G221" s="70"/>
       <c r="H221" s="24"/>
       <c r="I221" s="34"/>
       <c r="J221" s="34"/>
@@ -6499,7 +6502,7 @@
       </c>
     </row>
     <row r="222" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G222" s="73"/>
+      <c r="G222" s="70"/>
       <c r="H222" s="24"/>
       <c r="I222" s="34"/>
       <c r="J222" s="34"/>
@@ -6518,7 +6521,7 @@
       </c>
     </row>
     <row r="223" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G223" s="73"/>
+      <c r="G223" s="70"/>
       <c r="H223" s="24"/>
       <c r="I223" s="34"/>
       <c r="J223" s="34"/>
@@ -6537,7 +6540,7 @@
       </c>
     </row>
     <row r="224" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G224" s="73"/>
+      <c r="G224" s="70"/>
       <c r="H224" s="24"/>
       <c r="I224" s="34"/>
       <c r="J224" s="34"/>
@@ -6556,7 +6559,7 @@
       </c>
     </row>
     <row r="225" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G225" s="73"/>
+      <c r="G225" s="70"/>
       <c r="H225" s="24"/>
       <c r="I225" s="34"/>
       <c r="J225" s="34"/>
@@ -6575,7 +6578,7 @@
       </c>
     </row>
     <row r="226" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G226" s="73"/>
+      <c r="G226" s="70"/>
       <c r="H226" s="24"/>
       <c r="I226" s="34"/>
       <c r="J226" s="34"/>
@@ -6594,7 +6597,7 @@
       </c>
     </row>
     <row r="227" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G227" s="73"/>
+      <c r="G227" s="70"/>
       <c r="H227" s="24"/>
       <c r="I227" s="34"/>
       <c r="J227" s="34"/>
@@ -6613,7 +6616,7 @@
       </c>
     </row>
     <row r="228" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G228" s="73"/>
+      <c r="G228" s="70"/>
       <c r="H228" s="24"/>
       <c r="I228" s="34"/>
       <c r="J228" s="34"/>
@@ -6632,7 +6635,7 @@
       </c>
     </row>
     <row r="229" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G229" s="73"/>
+      <c r="G229" s="70"/>
       <c r="H229" s="24"/>
       <c r="I229" s="34"/>
       <c r="J229" s="34"/>
@@ -6651,7 +6654,7 @@
       </c>
     </row>
     <row r="230" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G230" s="73"/>
+      <c r="G230" s="70"/>
       <c r="H230" s="24"/>
       <c r="I230" s="34"/>
       <c r="J230" s="34"/>
@@ -6670,7 +6673,7 @@
       </c>
     </row>
     <row r="231" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G231" s="73"/>
+      <c r="G231" s="70"/>
       <c r="H231" s="24"/>
       <c r="I231" s="34"/>
       <c r="J231" s="34"/>
@@ -6689,7 +6692,7 @@
       </c>
     </row>
     <row r="232" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G232" s="73"/>
+      <c r="G232" s="70"/>
       <c r="H232" s="24"/>
       <c r="I232" s="34"/>
       <c r="J232" s="34"/>
@@ -6708,7 +6711,7 @@
       </c>
     </row>
     <row r="233" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G233" s="73"/>
+      <c r="G233" s="70"/>
       <c r="H233" s="24"/>
       <c r="I233" s="34"/>
       <c r="J233" s="34"/>
@@ -6727,7 +6730,7 @@
       </c>
     </row>
     <row r="234" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G234" s="73"/>
+      <c r="G234" s="70"/>
       <c r="H234" s="24"/>
       <c r="I234" s="34"/>
       <c r="J234" s="34"/>
@@ -6746,7 +6749,7 @@
       </c>
     </row>
     <row r="235" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G235" s="73"/>
+      <c r="G235" s="70"/>
       <c r="H235" s="24"/>
       <c r="I235" s="34"/>
       <c r="J235" s="34"/>
@@ -6765,7 +6768,7 @@
       </c>
     </row>
     <row r="236" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G236" s="73"/>
+      <c r="G236" s="70"/>
       <c r="H236" s="24"/>
       <c r="I236" s="34"/>
       <c r="J236" s="34"/>
@@ -6784,7 +6787,7 @@
       </c>
     </row>
     <row r="237" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G237" s="73"/>
+      <c r="G237" s="70"/>
       <c r="H237" s="24"/>
       <c r="I237" s="34"/>
       <c r="J237" s="34"/>
@@ -6803,7 +6806,7 @@
       </c>
     </row>
     <row r="238" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G238" s="73"/>
+      <c r="G238" s="70"/>
       <c r="H238" s="24"/>
       <c r="I238" s="34"/>
       <c r="J238" s="34"/>
@@ -6822,7 +6825,7 @@
       </c>
     </row>
     <row r="239" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G239" s="73"/>
+      <c r="G239" s="70"/>
       <c r="H239" s="24"/>
       <c r="I239" s="34"/>
       <c r="J239" s="34"/>
@@ -6841,7 +6844,7 @@
       </c>
     </row>
     <row r="240" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G240" s="73"/>
+      <c r="G240" s="70"/>
       <c r="H240" s="24"/>
       <c r="I240" s="34"/>
       <c r="J240" s="34"/>
@@ -6860,7 +6863,7 @@
       </c>
     </row>
     <row r="241" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G241" s="73"/>
+      <c r="G241" s="70"/>
       <c r="H241" s="24"/>
       <c r="I241" s="34"/>
       <c r="J241" s="34"/>
@@ -6879,7 +6882,7 @@
       </c>
     </row>
     <row r="242" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G242" s="73"/>
+      <c r="G242" s="70"/>
       <c r="H242" s="24"/>
       <c r="I242" s="34"/>
       <c r="J242" s="34"/>
@@ -6898,7 +6901,7 @@
       </c>
     </row>
     <row r="243" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G243" s="73"/>
+      <c r="G243" s="70"/>
       <c r="H243" s="24"/>
       <c r="I243" s="34"/>
       <c r="J243" s="34"/>
@@ -6917,7 +6920,7 @@
       </c>
     </row>
     <row r="244" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G244" s="73"/>
+      <c r="G244" s="70"/>
       <c r="H244" s="24"/>
       <c r="I244" s="34"/>
       <c r="J244" s="34"/>
@@ -6936,7 +6939,7 @@
       </c>
     </row>
     <row r="245" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G245" s="73"/>
+      <c r="G245" s="70"/>
       <c r="H245" s="24"/>
       <c r="I245" s="34"/>
       <c r="J245" s="34"/>
@@ -6955,7 +6958,7 @@
       </c>
     </row>
     <row r="246" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G246" s="73"/>
+      <c r="G246" s="70"/>
       <c r="H246" s="24"/>
       <c r="I246" s="34"/>
       <c r="J246" s="34"/>
@@ -6974,7 +6977,7 @@
       </c>
     </row>
     <row r="247" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G247" s="73"/>
+      <c r="G247" s="70"/>
       <c r="H247" s="24"/>
       <c r="I247" s="34"/>
       <c r="J247" s="34"/>
@@ -6993,7 +6996,7 @@
       </c>
     </row>
     <row r="248" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G248" s="73"/>
+      <c r="G248" s="70"/>
       <c r="H248" s="24"/>
       <c r="I248" s="34"/>
       <c r="J248" s="34"/>
@@ -7012,7 +7015,7 @@
       </c>
     </row>
     <row r="249" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G249" s="73"/>
+      <c r="G249" s="70"/>
       <c r="H249" s="24"/>
       <c r="I249" s="34"/>
       <c r="J249" s="34"/>
@@ -7031,7 +7034,7 @@
       </c>
     </row>
     <row r="250" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G250" s="73"/>
+      <c r="G250" s="70"/>
       <c r="H250" s="24"/>
       <c r="I250" s="34"/>
       <c r="J250" s="34"/>
@@ -7050,7 +7053,7 @@
       </c>
     </row>
     <row r="251" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G251" s="73"/>
+      <c r="G251" s="70"/>
       <c r="H251" s="24"/>
       <c r="I251" s="34"/>
       <c r="J251" s="34"/>
@@ -7069,7 +7072,7 @@
       </c>
     </row>
     <row r="252" spans="7:15" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G252" s="74"/>
+      <c r="G252" s="71"/>
       <c r="H252" s="36"/>
       <c r="I252" s="37"/>
       <c r="J252" s="37"/>
@@ -7108,19 +7111,19 @@
     </row>
     <row r="255" spans="7:15" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="256" spans="7:15" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="H256" s="69" t="s">
+      <c r="H256" s="72" t="s">
         <v>49</v>
       </c>
-      <c r="I256" s="70"/>
-      <c r="J256" s="70"/>
-      <c r="K256" s="70"/>
-      <c r="L256" s="70"/>
-      <c r="M256" s="70"/>
-      <c r="N256" s="70"/>
-      <c r="O256" s="71"/>
+      <c r="I256" s="73"/>
+      <c r="J256" s="73"/>
+      <c r="K256" s="73"/>
+      <c r="L256" s="73"/>
+      <c r="M256" s="73"/>
+      <c r="N256" s="73"/>
+      <c r="O256" s="74"/>
     </row>
     <row r="257" spans="7:18" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="G257" s="72" t="s">
+      <c r="G257" s="69" t="s">
         <v>50</v>
       </c>
       <c r="H257" s="56" t="s">
@@ -7149,7 +7152,7 @@
       </c>
     </row>
     <row r="258" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G258" s="73"/>
+      <c r="G258" s="70"/>
       <c r="H258" s="53"/>
       <c r="I258" s="54"/>
       <c r="J258" s="54"/>
@@ -7168,7 +7171,7 @@
       </c>
     </row>
     <row r="259" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G259" s="73"/>
+      <c r="G259" s="70"/>
       <c r="H259" s="53"/>
       <c r="I259" s="34"/>
       <c r="J259" s="34"/>
@@ -7187,7 +7190,7 @@
       </c>
     </row>
     <row r="260" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G260" s="73"/>
+      <c r="G260" s="70"/>
       <c r="H260" s="53"/>
       <c r="I260" s="34"/>
       <c r="J260" s="34"/>
@@ -7206,7 +7209,7 @@
       </c>
     </row>
     <row r="261" spans="7:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G261" s="73"/>
+      <c r="G261" s="70"/>
       <c r="H261" s="53"/>
       <c r="I261" s="34"/>
       <c r="J261" s="34"/>
@@ -7225,7 +7228,7 @@
       </c>
     </row>
     <row r="262" spans="7:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G262" s="73"/>
+      <c r="G262" s="70"/>
       <c r="H262" s="53"/>
       <c r="I262" s="34"/>
       <c r="J262" s="34"/>
@@ -7242,13 +7245,13 @@
         <f t="shared" si="13"/>
         <v>1423</v>
       </c>
-      <c r="Q262" s="75" t="s">
+      <c r="Q262" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="R262" s="76"/>
+      <c r="R262" s="80"/>
     </row>
     <row r="263" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G263" s="73"/>
+      <c r="G263" s="70"/>
       <c r="H263" s="53"/>
       <c r="I263" s="34"/>
       <c r="J263" s="34"/>
@@ -7271,7 +7274,7 @@
       <c r="R263" s="62"/>
     </row>
     <row r="264" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G264" s="73"/>
+      <c r="G264" s="70"/>
       <c r="H264" s="53"/>
       <c r="I264" s="34"/>
       <c r="J264" s="34"/>
@@ -7294,7 +7297,7 @@
       <c r="R264" s="64"/>
     </row>
     <row r="265" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G265" s="73"/>
+      <c r="G265" s="70"/>
       <c r="H265" s="53"/>
       <c r="I265" s="34"/>
       <c r="J265" s="34"/>
@@ -7317,7 +7320,7 @@
       <c r="R265" s="64"/>
     </row>
     <row r="266" spans="7:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G266" s="73"/>
+      <c r="G266" s="70"/>
       <c r="H266" s="43"/>
       <c r="I266" s="34"/>
       <c r="J266" s="34"/>
@@ -7340,7 +7343,7 @@
       <c r="R266" s="66"/>
     </row>
     <row r="267" spans="7:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G267" s="73"/>
+      <c r="G267" s="70"/>
       <c r="H267" s="43"/>
       <c r="I267" s="34"/>
       <c r="J267" s="34"/>
@@ -7366,7 +7369,7 @@
       </c>
     </row>
     <row r="268" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G268" s="73"/>
+      <c r="G268" s="70"/>
       <c r="H268" s="43"/>
       <c r="I268" s="34"/>
       <c r="J268" s="34"/>
@@ -7385,7 +7388,7 @@
       </c>
     </row>
     <row r="269" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G269" s="73"/>
+      <c r="G269" s="70"/>
       <c r="H269" s="43"/>
       <c r="I269" s="34"/>
       <c r="J269" s="34"/>
@@ -7404,7 +7407,7 @@
       </c>
     </row>
     <row r="270" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G270" s="73"/>
+      <c r="G270" s="70"/>
       <c r="H270" s="43"/>
       <c r="I270" s="34"/>
       <c r="J270" s="34"/>
@@ -7423,7 +7426,7 @@
       </c>
     </row>
     <row r="271" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G271" s="73"/>
+      <c r="G271" s="70"/>
       <c r="H271" s="43"/>
       <c r="I271" s="34"/>
       <c r="J271" s="34"/>
@@ -7442,7 +7445,7 @@
       </c>
     </row>
     <row r="272" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G272" s="73"/>
+      <c r="G272" s="70"/>
       <c r="H272" s="43"/>
       <c r="I272" s="34"/>
       <c r="J272" s="34"/>
@@ -7461,7 +7464,7 @@
       </c>
     </row>
     <row r="273" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G273" s="73"/>
+      <c r="G273" s="70"/>
       <c r="H273" s="43"/>
       <c r="I273" s="34"/>
       <c r="J273" s="34"/>
@@ -7480,7 +7483,7 @@
       </c>
     </row>
     <row r="274" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G274" s="73"/>
+      <c r="G274" s="70"/>
       <c r="H274" s="43"/>
       <c r="I274" s="34"/>
       <c r="J274" s="34"/>
@@ -7499,7 +7502,7 @@
       </c>
     </row>
     <row r="275" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G275" s="73"/>
+      <c r="G275" s="70"/>
       <c r="H275" s="24"/>
       <c r="I275" s="34"/>
       <c r="J275" s="34"/>
@@ -7518,7 +7521,7 @@
       </c>
     </row>
     <row r="276" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G276" s="73"/>
+      <c r="G276" s="70"/>
       <c r="H276" s="24"/>
       <c r="I276" s="34"/>
       <c r="J276" s="34"/>
@@ -7537,7 +7540,7 @@
       </c>
     </row>
     <row r="277" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G277" s="73"/>
+      <c r="G277" s="70"/>
       <c r="H277" s="24"/>
       <c r="I277" s="34"/>
       <c r="J277" s="34"/>
@@ -7556,7 +7559,7 @@
       </c>
     </row>
     <row r="278" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G278" s="73"/>
+      <c r="G278" s="70"/>
       <c r="H278" s="24"/>
       <c r="I278" s="34"/>
       <c r="J278" s="34"/>
@@ -7575,7 +7578,7 @@
       </c>
     </row>
     <row r="279" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G279" s="73"/>
+      <c r="G279" s="70"/>
       <c r="H279" s="24"/>
       <c r="I279" s="34"/>
       <c r="J279" s="34"/>
@@ -7594,7 +7597,7 @@
       </c>
     </row>
     <row r="280" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G280" s="73"/>
+      <c r="G280" s="70"/>
       <c r="H280" s="24"/>
       <c r="I280" s="34"/>
       <c r="J280" s="34"/>
@@ -7613,7 +7616,7 @@
       </c>
     </row>
     <row r="281" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G281" s="73"/>
+      <c r="G281" s="70"/>
       <c r="H281" s="24"/>
       <c r="I281" s="34"/>
       <c r="J281" s="34"/>
@@ -7632,7 +7635,7 @@
       </c>
     </row>
     <row r="282" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G282" s="73"/>
+      <c r="G282" s="70"/>
       <c r="H282" s="24"/>
       <c r="I282" s="34"/>
       <c r="J282" s="34"/>
@@ -7651,7 +7654,7 @@
       </c>
     </row>
     <row r="283" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G283" s="73"/>
+      <c r="G283" s="70"/>
       <c r="H283" s="24"/>
       <c r="I283" s="34"/>
       <c r="J283" s="34"/>
@@ -7670,7 +7673,7 @@
       </c>
     </row>
     <row r="284" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G284" s="73"/>
+      <c r="G284" s="70"/>
       <c r="H284" s="24"/>
       <c r="I284" s="34"/>
       <c r="J284" s="34"/>
@@ -7689,7 +7692,7 @@
       </c>
     </row>
     <row r="285" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G285" s="73"/>
+      <c r="G285" s="70"/>
       <c r="H285" s="24"/>
       <c r="I285" s="34"/>
       <c r="J285" s="34"/>
@@ -7708,7 +7711,7 @@
       </c>
     </row>
     <row r="286" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G286" s="73"/>
+      <c r="G286" s="70"/>
       <c r="H286" s="24"/>
       <c r="I286" s="34"/>
       <c r="J286" s="34"/>
@@ -7727,7 +7730,7 @@
       </c>
     </row>
     <row r="287" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G287" s="73"/>
+      <c r="G287" s="70"/>
       <c r="H287" s="24"/>
       <c r="I287" s="34"/>
       <c r="J287" s="34"/>
@@ -7746,7 +7749,7 @@
       </c>
     </row>
     <row r="288" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G288" s="73"/>
+      <c r="G288" s="70"/>
       <c r="H288" s="24"/>
       <c r="I288" s="34"/>
       <c r="J288" s="34"/>
@@ -7765,7 +7768,7 @@
       </c>
     </row>
     <row r="289" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G289" s="73"/>
+      <c r="G289" s="70"/>
       <c r="H289" s="24"/>
       <c r="I289" s="34"/>
       <c r="J289" s="34"/>
@@ -7784,7 +7787,7 @@
       </c>
     </row>
     <row r="290" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G290" s="73"/>
+      <c r="G290" s="70"/>
       <c r="H290" s="24"/>
       <c r="I290" s="34"/>
       <c r="J290" s="34"/>
@@ -7803,7 +7806,7 @@
       </c>
     </row>
     <row r="291" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G291" s="73"/>
+      <c r="G291" s="70"/>
       <c r="H291" s="24"/>
       <c r="I291" s="34"/>
       <c r="J291" s="34"/>
@@ -7822,7 +7825,7 @@
       </c>
     </row>
     <row r="292" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G292" s="73"/>
+      <c r="G292" s="70"/>
       <c r="H292" s="24"/>
       <c r="I292" s="34"/>
       <c r="J292" s="34"/>
@@ -7841,7 +7844,7 @@
       </c>
     </row>
     <row r="293" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G293" s="73"/>
+      <c r="G293" s="70"/>
       <c r="H293" s="24"/>
       <c r="I293" s="34"/>
       <c r="J293" s="34"/>
@@ -7860,7 +7863,7 @@
       </c>
     </row>
     <row r="294" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G294" s="73"/>
+      <c r="G294" s="70"/>
       <c r="H294" s="24"/>
       <c r="I294" s="34"/>
       <c r="J294" s="34"/>
@@ -7879,7 +7882,7 @@
       </c>
     </row>
     <row r="295" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G295" s="73"/>
+      <c r="G295" s="70"/>
       <c r="H295" s="24"/>
       <c r="I295" s="34"/>
       <c r="J295" s="34"/>
@@ -7898,7 +7901,7 @@
       </c>
     </row>
     <row r="296" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G296" s="73"/>
+      <c r="G296" s="70"/>
       <c r="H296" s="24"/>
       <c r="I296" s="34"/>
       <c r="J296" s="34"/>
@@ -7917,7 +7920,7 @@
       </c>
     </row>
     <row r="297" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G297" s="73"/>
+      <c r="G297" s="70"/>
       <c r="H297" s="24"/>
       <c r="I297" s="34"/>
       <c r="J297" s="34"/>
@@ -7936,7 +7939,7 @@
       </c>
     </row>
     <row r="298" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G298" s="73"/>
+      <c r="G298" s="70"/>
       <c r="H298" s="24"/>
       <c r="I298" s="34"/>
       <c r="J298" s="34"/>
@@ -7955,7 +7958,7 @@
       </c>
     </row>
     <row r="299" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G299" s="73"/>
+      <c r="G299" s="70"/>
       <c r="H299" s="24"/>
       <c r="I299" s="34"/>
       <c r="J299" s="34"/>
@@ -7974,7 +7977,7 @@
       </c>
     </row>
     <row r="300" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G300" s="73"/>
+      <c r="G300" s="70"/>
       <c r="H300" s="24"/>
       <c r="I300" s="34"/>
       <c r="J300" s="34"/>
@@ -7993,7 +7996,7 @@
       </c>
     </row>
     <row r="301" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G301" s="73"/>
+      <c r="G301" s="70"/>
       <c r="H301" s="24"/>
       <c r="I301" s="34"/>
       <c r="J301" s="34"/>
@@ -8012,7 +8015,7 @@
       </c>
     </row>
     <row r="302" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G302" s="73"/>
+      <c r="G302" s="70"/>
       <c r="H302" s="24"/>
       <c r="I302" s="34"/>
       <c r="J302" s="34"/>
@@ -8031,7 +8034,7 @@
       </c>
     </row>
     <row r="303" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G303" s="73"/>
+      <c r="G303" s="70"/>
       <c r="H303" s="24"/>
       <c r="I303" s="34"/>
       <c r="J303" s="34"/>
@@ -8050,7 +8053,7 @@
       </c>
     </row>
     <row r="304" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G304" s="73"/>
+      <c r="G304" s="70"/>
       <c r="H304" s="24"/>
       <c r="I304" s="34"/>
       <c r="J304" s="34"/>
@@ -8069,7 +8072,7 @@
       </c>
     </row>
     <row r="305" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G305" s="73"/>
+      <c r="G305" s="70"/>
       <c r="H305" s="24"/>
       <c r="I305" s="34"/>
       <c r="J305" s="34"/>
@@ -8088,7 +8091,7 @@
       </c>
     </row>
     <row r="306" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G306" s="73"/>
+      <c r="G306" s="70"/>
       <c r="H306" s="24"/>
       <c r="I306" s="34"/>
       <c r="J306" s="34"/>
@@ -8107,7 +8110,7 @@
       </c>
     </row>
     <row r="307" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G307" s="73"/>
+      <c r="G307" s="70"/>
       <c r="H307" s="24"/>
       <c r="I307" s="34"/>
       <c r="J307" s="34"/>
@@ -8126,7 +8129,7 @@
       </c>
     </row>
     <row r="308" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G308" s="73"/>
+      <c r="G308" s="70"/>
       <c r="H308" s="24"/>
       <c r="I308" s="34"/>
       <c r="J308" s="34"/>
@@ -8145,7 +8148,7 @@
       </c>
     </row>
     <row r="309" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G309" s="73"/>
+      <c r="G309" s="70"/>
       <c r="H309" s="24"/>
       <c r="I309" s="34"/>
       <c r="J309" s="34"/>
@@ -8164,7 +8167,7 @@
       </c>
     </row>
     <row r="310" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G310" s="73"/>
+      <c r="G310" s="70"/>
       <c r="H310" s="24"/>
       <c r="I310" s="34"/>
       <c r="J310" s="34"/>
@@ -8183,7 +8186,7 @@
       </c>
     </row>
     <row r="311" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G311" s="73"/>
+      <c r="G311" s="70"/>
       <c r="H311" s="24"/>
       <c r="I311" s="34"/>
       <c r="J311" s="34"/>
@@ -8202,7 +8205,7 @@
       </c>
     </row>
     <row r="312" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G312" s="73"/>
+      <c r="G312" s="70"/>
       <c r="H312" s="24"/>
       <c r="I312" s="34"/>
       <c r="J312" s="34"/>
@@ -8221,7 +8224,7 @@
       </c>
     </row>
     <row r="313" spans="7:15" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G313" s="74"/>
+      <c r="G313" s="71"/>
       <c r="H313" s="36"/>
       <c r="I313" s="37"/>
       <c r="J313" s="37"/>
@@ -8260,19 +8263,19 @@
     </row>
     <row r="316" spans="7:15" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="317" spans="7:15" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="H317" s="69" t="s">
+      <c r="H317" s="72" t="s">
         <v>51</v>
       </c>
-      <c r="I317" s="70"/>
-      <c r="J317" s="70"/>
-      <c r="K317" s="70"/>
-      <c r="L317" s="70"/>
-      <c r="M317" s="70"/>
-      <c r="N317" s="70"/>
-      <c r="O317" s="71"/>
+      <c r="I317" s="73"/>
+      <c r="J317" s="73"/>
+      <c r="K317" s="73"/>
+      <c r="L317" s="73"/>
+      <c r="M317" s="73"/>
+      <c r="N317" s="73"/>
+      <c r="O317" s="74"/>
     </row>
     <row r="318" spans="7:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="G318" s="72" t="s">
+      <c r="G318" s="69" t="s">
         <v>52</v>
       </c>
       <c r="H318" s="56" t="s">
@@ -8301,7 +8304,7 @@
       </c>
     </row>
     <row r="319" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G319" s="73"/>
+      <c r="G319" s="70"/>
       <c r="H319" s="53"/>
       <c r="I319" s="54"/>
       <c r="J319" s="54"/>
@@ -8320,7 +8323,7 @@
       </c>
     </row>
     <row r="320" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G320" s="73"/>
+      <c r="G320" s="70"/>
       <c r="H320" s="53"/>
       <c r="I320" s="34"/>
       <c r="J320" s="34"/>
@@ -8339,7 +8342,7 @@
       </c>
     </row>
     <row r="321" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G321" s="73"/>
+      <c r="G321" s="70"/>
       <c r="H321" s="53"/>
       <c r="I321" s="34"/>
       <c r="J321" s="34"/>
@@ -8358,7 +8361,7 @@
       </c>
     </row>
     <row r="322" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G322" s="73"/>
+      <c r="G322" s="70"/>
       <c r="H322" s="53"/>
       <c r="I322" s="34"/>
       <c r="J322" s="34"/>
@@ -8377,7 +8380,7 @@
       </c>
     </row>
     <row r="323" spans="7:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G323" s="73"/>
+      <c r="G323" s="70"/>
       <c r="H323" s="53"/>
       <c r="I323" s="34"/>
       <c r="J323" s="34"/>
@@ -8396,7 +8399,7 @@
       </c>
     </row>
     <row r="324" spans="7:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G324" s="73"/>
+      <c r="G324" s="70"/>
       <c r="H324" s="53"/>
       <c r="I324" s="34"/>
       <c r="J324" s="34"/>
@@ -8413,13 +8416,13 @@
         <f t="shared" si="15"/>
         <v>1423</v>
       </c>
-      <c r="Q324" s="75" t="s">
+      <c r="Q324" s="79" t="s">
         <v>68</v>
       </c>
-      <c r="R324" s="76"/>
+      <c r="R324" s="80"/>
     </row>
     <row r="325" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G325" s="73"/>
+      <c r="G325" s="70"/>
       <c r="H325" s="53"/>
       <c r="I325" s="34"/>
       <c r="J325" s="34"/>
@@ -8442,7 +8445,7 @@
       <c r="R325" s="62"/>
     </row>
     <row r="326" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G326" s="73"/>
+      <c r="G326" s="70"/>
       <c r="H326" s="53"/>
       <c r="I326" s="34"/>
       <c r="J326" s="34"/>
@@ -8465,7 +8468,7 @@
       <c r="R326" s="64"/>
     </row>
     <row r="327" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G327" s="73"/>
+      <c r="G327" s="70"/>
       <c r="H327" s="43"/>
       <c r="I327" s="34"/>
       <c r="J327" s="34"/>
@@ -8488,7 +8491,7 @@
       <c r="R327" s="64"/>
     </row>
     <row r="328" spans="7:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G328" s="73"/>
+      <c r="G328" s="70"/>
       <c r="H328" s="43"/>
       <c r="I328" s="34"/>
       <c r="J328" s="34"/>
@@ -8511,7 +8514,7 @@
       <c r="R328" s="66"/>
     </row>
     <row r="329" spans="7:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G329" s="73"/>
+      <c r="G329" s="70"/>
       <c r="H329" s="43"/>
       <c r="I329" s="34"/>
       <c r="J329" s="34"/>
@@ -8537,7 +8540,7 @@
       </c>
     </row>
     <row r="330" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G330" s="73"/>
+      <c r="G330" s="70"/>
       <c r="H330" s="43"/>
       <c r="I330" s="34"/>
       <c r="J330" s="34"/>
@@ -8556,7 +8559,7 @@
       </c>
     </row>
     <row r="331" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G331" s="73"/>
+      <c r="G331" s="70"/>
       <c r="H331" s="43"/>
       <c r="I331" s="34"/>
       <c r="J331" s="34"/>
@@ -8575,7 +8578,7 @@
       </c>
     </row>
     <row r="332" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G332" s="73"/>
+      <c r="G332" s="70"/>
       <c r="H332" s="43"/>
       <c r="I332" s="34"/>
       <c r="J332" s="34"/>
@@ -8594,7 +8597,7 @@
       </c>
     </row>
     <row r="333" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G333" s="73"/>
+      <c r="G333" s="70"/>
       <c r="H333" s="43"/>
       <c r="I333" s="34"/>
       <c r="J333" s="34"/>
@@ -8613,7 +8616,7 @@
       </c>
     </row>
     <row r="334" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G334" s="73"/>
+      <c r="G334" s="70"/>
       <c r="H334" s="43"/>
       <c r="I334" s="34"/>
       <c r="J334" s="34"/>
@@ -8632,7 +8635,7 @@
       </c>
     </row>
     <row r="335" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G335" s="73"/>
+      <c r="G335" s="70"/>
       <c r="H335" s="43"/>
       <c r="I335" s="34"/>
       <c r="J335" s="34"/>
@@ -8651,7 +8654,7 @@
       </c>
     </row>
     <row r="336" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G336" s="73"/>
+      <c r="G336" s="70"/>
       <c r="H336" s="24"/>
       <c r="I336" s="34"/>
       <c r="J336" s="34"/>
@@ -8670,7 +8673,7 @@
       </c>
     </row>
     <row r="337" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G337" s="73"/>
+      <c r="G337" s="70"/>
       <c r="H337" s="24"/>
       <c r="I337" s="34"/>
       <c r="J337" s="34"/>
@@ -8689,7 +8692,7 @@
       </c>
     </row>
     <row r="338" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G338" s="73"/>
+      <c r="G338" s="70"/>
       <c r="H338" s="24"/>
       <c r="I338" s="34"/>
       <c r="J338" s="34"/>
@@ -8708,7 +8711,7 @@
       </c>
     </row>
     <row r="339" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G339" s="73"/>
+      <c r="G339" s="70"/>
       <c r="H339" s="24"/>
       <c r="I339" s="34"/>
       <c r="J339" s="34"/>
@@ -8727,7 +8730,7 @@
       </c>
     </row>
     <row r="340" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G340" s="73"/>
+      <c r="G340" s="70"/>
       <c r="H340" s="24"/>
       <c r="I340" s="34"/>
       <c r="J340" s="34"/>
@@ -8746,7 +8749,7 @@
       </c>
     </row>
     <row r="341" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G341" s="73"/>
+      <c r="G341" s="70"/>
       <c r="H341" s="24"/>
       <c r="I341" s="34"/>
       <c r="J341" s="34"/>
@@ -8765,7 +8768,7 @@
       </c>
     </row>
     <row r="342" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G342" s="73"/>
+      <c r="G342" s="70"/>
       <c r="H342" s="24"/>
       <c r="I342" s="34"/>
       <c r="J342" s="34"/>
@@ -8784,7 +8787,7 @@
       </c>
     </row>
     <row r="343" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G343" s="73"/>
+      <c r="G343" s="70"/>
       <c r="H343" s="24"/>
       <c r="I343" s="34"/>
       <c r="J343" s="34"/>
@@ -8803,7 +8806,7 @@
       </c>
     </row>
     <row r="344" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G344" s="73"/>
+      <c r="G344" s="70"/>
       <c r="H344" s="24"/>
       <c r="I344" s="34"/>
       <c r="J344" s="34"/>
@@ -8822,7 +8825,7 @@
       </c>
     </row>
     <row r="345" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G345" s="73"/>
+      <c r="G345" s="70"/>
       <c r="H345" s="24"/>
       <c r="I345" s="34"/>
       <c r="J345" s="34"/>
@@ -8841,7 +8844,7 @@
       </c>
     </row>
     <row r="346" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G346" s="73"/>
+      <c r="G346" s="70"/>
       <c r="H346" s="24"/>
       <c r="I346" s="34"/>
       <c r="J346" s="34"/>
@@ -8860,7 +8863,7 @@
       </c>
     </row>
     <row r="347" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G347" s="73"/>
+      <c r="G347" s="70"/>
       <c r="H347" s="24"/>
       <c r="I347" s="34"/>
       <c r="J347" s="34"/>
@@ -8879,7 +8882,7 @@
       </c>
     </row>
     <row r="348" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G348" s="73"/>
+      <c r="G348" s="70"/>
       <c r="H348" s="24"/>
       <c r="I348" s="34"/>
       <c r="J348" s="34"/>
@@ -8898,7 +8901,7 @@
       </c>
     </row>
     <row r="349" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G349" s="73"/>
+      <c r="G349" s="70"/>
       <c r="H349" s="24"/>
       <c r="I349" s="34"/>
       <c r="J349" s="34"/>
@@ -8917,7 +8920,7 @@
       </c>
     </row>
     <row r="350" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G350" s="73"/>
+      <c r="G350" s="70"/>
       <c r="H350" s="24"/>
       <c r="I350" s="34"/>
       <c r="J350" s="34"/>
@@ -8936,7 +8939,7 @@
       </c>
     </row>
     <row r="351" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G351" s="73"/>
+      <c r="G351" s="70"/>
       <c r="H351" s="24"/>
       <c r="I351" s="34"/>
       <c r="J351" s="34"/>
@@ -8955,7 +8958,7 @@
       </c>
     </row>
     <row r="352" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G352" s="73"/>
+      <c r="G352" s="70"/>
       <c r="H352" s="24"/>
       <c r="I352" s="34"/>
       <c r="J352" s="34"/>
@@ -8974,7 +8977,7 @@
       </c>
     </row>
     <row r="353" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G353" s="73"/>
+      <c r="G353" s="70"/>
       <c r="H353" s="24"/>
       <c r="I353" s="34"/>
       <c r="J353" s="34"/>
@@ -8993,7 +8996,7 @@
       </c>
     </row>
     <row r="354" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G354" s="73"/>
+      <c r="G354" s="70"/>
       <c r="H354" s="24"/>
       <c r="I354" s="34"/>
       <c r="J354" s="34"/>
@@ -9012,7 +9015,7 @@
       </c>
     </row>
     <row r="355" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G355" s="73"/>
+      <c r="G355" s="70"/>
       <c r="H355" s="24"/>
       <c r="I355" s="34"/>
       <c r="J355" s="34"/>
@@ -9031,7 +9034,7 @@
       </c>
     </row>
     <row r="356" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G356" s="73"/>
+      <c r="G356" s="70"/>
       <c r="H356" s="24"/>
       <c r="I356" s="34"/>
       <c r="J356" s="34"/>
@@ -9050,7 +9053,7 @@
       </c>
     </row>
     <row r="357" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G357" s="73"/>
+      <c r="G357" s="70"/>
       <c r="H357" s="24"/>
       <c r="I357" s="34"/>
       <c r="J357" s="34"/>
@@ -9069,7 +9072,7 @@
       </c>
     </row>
     <row r="358" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G358" s="73"/>
+      <c r="G358" s="70"/>
       <c r="H358" s="24"/>
       <c r="I358" s="34"/>
       <c r="J358" s="34"/>
@@ -9088,7 +9091,7 @@
       </c>
     </row>
     <row r="359" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G359" s="73"/>
+      <c r="G359" s="70"/>
       <c r="H359" s="24"/>
       <c r="I359" s="34"/>
       <c r="J359" s="34"/>
@@ -9107,7 +9110,7 @@
       </c>
     </row>
     <row r="360" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G360" s="73"/>
+      <c r="G360" s="70"/>
       <c r="H360" s="24"/>
       <c r="I360" s="34"/>
       <c r="J360" s="34"/>
@@ -9126,7 +9129,7 @@
       </c>
     </row>
     <row r="361" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G361" s="73"/>
+      <c r="G361" s="70"/>
       <c r="H361" s="24"/>
       <c r="I361" s="34"/>
       <c r="J361" s="34"/>
@@ -9145,7 +9148,7 @@
       </c>
     </row>
     <row r="362" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G362" s="73"/>
+      <c r="G362" s="70"/>
       <c r="H362" s="24"/>
       <c r="I362" s="34"/>
       <c r="J362" s="34"/>
@@ -9164,7 +9167,7 @@
       </c>
     </row>
     <row r="363" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G363" s="73"/>
+      <c r="G363" s="70"/>
       <c r="H363" s="24"/>
       <c r="I363" s="34"/>
       <c r="J363" s="34"/>
@@ -9183,7 +9186,7 @@
       </c>
     </row>
     <row r="364" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G364" s="73"/>
+      <c r="G364" s="70"/>
       <c r="H364" s="24"/>
       <c r="I364" s="34"/>
       <c r="J364" s="34"/>
@@ -9202,7 +9205,7 @@
       </c>
     </row>
     <row r="365" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G365" s="73"/>
+      <c r="G365" s="70"/>
       <c r="H365" s="24"/>
       <c r="I365" s="34"/>
       <c r="J365" s="34"/>
@@ -9221,7 +9224,7 @@
       </c>
     </row>
     <row r="366" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G366" s="73"/>
+      <c r="G366" s="70"/>
       <c r="H366" s="24"/>
       <c r="I366" s="34"/>
       <c r="J366" s="34"/>
@@ -9240,7 +9243,7 @@
       </c>
     </row>
     <row r="367" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G367" s="73"/>
+      <c r="G367" s="70"/>
       <c r="H367" s="24"/>
       <c r="I367" s="34"/>
       <c r="J367" s="34"/>
@@ -9259,7 +9262,7 @@
       </c>
     </row>
     <row r="368" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G368" s="73"/>
+      <c r="G368" s="70"/>
       <c r="H368" s="24"/>
       <c r="I368" s="34"/>
       <c r="J368" s="34"/>
@@ -9278,7 +9281,7 @@
       </c>
     </row>
     <row r="369" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G369" s="73"/>
+      <c r="G369" s="70"/>
       <c r="H369" s="24"/>
       <c r="I369" s="34"/>
       <c r="J369" s="34"/>
@@ -9297,7 +9300,7 @@
       </c>
     </row>
     <row r="370" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G370" s="73"/>
+      <c r="G370" s="70"/>
       <c r="H370" s="24"/>
       <c r="I370" s="34"/>
       <c r="J370" s="34"/>
@@ -9316,7 +9319,7 @@
       </c>
     </row>
     <row r="371" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G371" s="73"/>
+      <c r="G371" s="70"/>
       <c r="H371" s="24"/>
       <c r="I371" s="34"/>
       <c r="J371" s="34"/>
@@ -9335,7 +9338,7 @@
       </c>
     </row>
     <row r="372" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G372" s="73"/>
+      <c r="G372" s="70"/>
       <c r="H372" s="24"/>
       <c r="I372" s="34"/>
       <c r="J372" s="34"/>
@@ -9354,7 +9357,7 @@
       </c>
     </row>
     <row r="373" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G373" s="73"/>
+      <c r="G373" s="70"/>
       <c r="H373" s="24"/>
       <c r="I373" s="34"/>
       <c r="J373" s="34"/>
@@ -9373,7 +9376,7 @@
       </c>
     </row>
     <row r="374" spans="7:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G374" s="74"/>
+      <c r="G374" s="71"/>
       <c r="H374" s="36"/>
       <c r="I374" s="37"/>
       <c r="J374" s="37"/>
@@ -9412,19 +9415,19 @@
     </row>
     <row r="377" spans="7:18" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="378" spans="7:18" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="H378" s="69" t="s">
+      <c r="H378" s="72" t="s">
         <v>53</v>
       </c>
-      <c r="I378" s="70"/>
-      <c r="J378" s="70"/>
-      <c r="K378" s="70"/>
-      <c r="L378" s="70"/>
-      <c r="M378" s="70"/>
-      <c r="N378" s="70"/>
-      <c r="O378" s="71"/>
+      <c r="I378" s="73"/>
+      <c r="J378" s="73"/>
+      <c r="K378" s="73"/>
+      <c r="L378" s="73"/>
+      <c r="M378" s="73"/>
+      <c r="N378" s="73"/>
+      <c r="O378" s="74"/>
     </row>
     <row r="379" spans="7:18" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="G379" s="72" t="s">
+      <c r="G379" s="69" t="s">
         <v>54</v>
       </c>
       <c r="H379" s="56" t="s">
@@ -9453,7 +9456,7 @@
       </c>
     </row>
     <row r="380" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G380" s="73"/>
+      <c r="G380" s="70"/>
       <c r="H380" s="53"/>
       <c r="I380" s="54"/>
       <c r="J380" s="54"/>
@@ -9472,7 +9475,7 @@
       </c>
     </row>
     <row r="381" spans="7:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G381" s="73"/>
+      <c r="G381" s="70"/>
       <c r="H381" s="53"/>
       <c r="I381" s="34"/>
       <c r="J381" s="34"/>
@@ -9491,7 +9494,7 @@
       </c>
     </row>
     <row r="382" spans="7:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G382" s="73"/>
+      <c r="G382" s="70"/>
       <c r="H382" s="53"/>
       <c r="I382" s="34"/>
       <c r="J382" s="34"/>
@@ -9508,13 +9511,13 @@
         <f t="shared" ref="O382:O435" si="17">O381+M382-N382</f>
         <v>1423</v>
       </c>
-      <c r="Q382" s="75" t="s">
+      <c r="Q382" s="79" t="s">
         <v>69</v>
       </c>
-      <c r="R382" s="76"/>
+      <c r="R382" s="80"/>
     </row>
     <row r="383" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G383" s="73"/>
+      <c r="G383" s="70"/>
       <c r="H383" s="53"/>
       <c r="I383" s="34"/>
       <c r="J383" s="34"/>
@@ -9537,7 +9540,7 @@
       <c r="R383" s="62"/>
     </row>
     <row r="384" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G384" s="73"/>
+      <c r="G384" s="70"/>
       <c r="H384" s="53"/>
       <c r="I384" s="34"/>
       <c r="J384" s="34"/>
@@ -9560,7 +9563,7 @@
       <c r="R384" s="64"/>
     </row>
     <row r="385" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G385" s="73"/>
+      <c r="G385" s="70"/>
       <c r="H385" s="53"/>
       <c r="I385" s="34"/>
       <c r="J385" s="34"/>
@@ -9583,7 +9586,7 @@
       <c r="R385" s="64"/>
     </row>
     <row r="386" spans="7:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G386" s="73"/>
+      <c r="G386" s="70"/>
       <c r="H386" s="53"/>
       <c r="I386" s="34"/>
       <c r="J386" s="34"/>
@@ -9606,7 +9609,7 @@
       <c r="R386" s="66"/>
     </row>
     <row r="387" spans="7:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G387" s="73"/>
+      <c r="G387" s="70"/>
       <c r="H387" s="53"/>
       <c r="I387" s="34"/>
       <c r="J387" s="34"/>
@@ -9632,7 +9635,7 @@
       </c>
     </row>
     <row r="388" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G388" s="73"/>
+      <c r="G388" s="70"/>
       <c r="H388" s="43"/>
       <c r="I388" s="34"/>
       <c r="J388" s="34"/>
@@ -9651,7 +9654,7 @@
       </c>
     </row>
     <row r="389" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G389" s="73"/>
+      <c r="G389" s="70"/>
       <c r="H389" s="43"/>
       <c r="I389" s="34"/>
       <c r="J389" s="34"/>
@@ -9670,7 +9673,7 @@
       </c>
     </row>
     <row r="390" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G390" s="73"/>
+      <c r="G390" s="70"/>
       <c r="H390" s="43"/>
       <c r="I390" s="34"/>
       <c r="J390" s="34"/>
@@ -9689,7 +9692,7 @@
       </c>
     </row>
     <row r="391" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G391" s="73"/>
+      <c r="G391" s="70"/>
       <c r="H391" s="43"/>
       <c r="I391" s="34"/>
       <c r="J391" s="34"/>
@@ -9708,7 +9711,7 @@
       </c>
     </row>
     <row r="392" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G392" s="73"/>
+      <c r="G392" s="70"/>
       <c r="H392" s="43"/>
       <c r="I392" s="34"/>
       <c r="J392" s="34"/>
@@ -9727,7 +9730,7 @@
       </c>
     </row>
     <row r="393" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G393" s="73"/>
+      <c r="G393" s="70"/>
       <c r="H393" s="43"/>
       <c r="I393" s="34"/>
       <c r="J393" s="34"/>
@@ -9746,7 +9749,7 @@
       </c>
     </row>
     <row r="394" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G394" s="73"/>
+      <c r="G394" s="70"/>
       <c r="H394" s="43"/>
       <c r="I394" s="34"/>
       <c r="J394" s="34"/>
@@ -9765,7 +9768,7 @@
       </c>
     </row>
     <row r="395" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G395" s="73"/>
+      <c r="G395" s="70"/>
       <c r="H395" s="43"/>
       <c r="I395" s="34"/>
       <c r="J395" s="34"/>
@@ -9784,7 +9787,7 @@
       </c>
     </row>
     <row r="396" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G396" s="73"/>
+      <c r="G396" s="70"/>
       <c r="H396" s="43"/>
       <c r="I396" s="34"/>
       <c r="J396" s="34"/>
@@ -9803,7 +9806,7 @@
       </c>
     </row>
     <row r="397" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G397" s="73"/>
+      <c r="G397" s="70"/>
       <c r="H397" s="24"/>
       <c r="I397" s="34"/>
       <c r="J397" s="34"/>
@@ -9822,7 +9825,7 @@
       </c>
     </row>
     <row r="398" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G398" s="73"/>
+      <c r="G398" s="70"/>
       <c r="H398" s="24"/>
       <c r="I398" s="34"/>
       <c r="J398" s="34"/>
@@ -9841,7 +9844,7 @@
       </c>
     </row>
     <row r="399" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G399" s="73"/>
+      <c r="G399" s="70"/>
       <c r="H399" s="24"/>
       <c r="I399" s="34"/>
       <c r="J399" s="34"/>
@@ -9860,7 +9863,7 @@
       </c>
     </row>
     <row r="400" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G400" s="73"/>
+      <c r="G400" s="70"/>
       <c r="H400" s="24"/>
       <c r="I400" s="34"/>
       <c r="J400" s="34"/>
@@ -9879,7 +9882,7 @@
       </c>
     </row>
     <row r="401" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G401" s="73"/>
+      <c r="G401" s="70"/>
       <c r="H401" s="24"/>
       <c r="I401" s="34"/>
       <c r="J401" s="34"/>
@@ -9898,7 +9901,7 @@
       </c>
     </row>
     <row r="402" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G402" s="73"/>
+      <c r="G402" s="70"/>
       <c r="H402" s="24"/>
       <c r="I402" s="34"/>
       <c r="J402" s="34"/>
@@ -9917,7 +9920,7 @@
       </c>
     </row>
     <row r="403" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G403" s="73"/>
+      <c r="G403" s="70"/>
       <c r="H403" s="24"/>
       <c r="I403" s="34"/>
       <c r="J403" s="34"/>
@@ -9936,7 +9939,7 @@
       </c>
     </row>
     <row r="404" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G404" s="73"/>
+      <c r="G404" s="70"/>
       <c r="H404" s="24"/>
       <c r="I404" s="34"/>
       <c r="J404" s="34"/>
@@ -9955,7 +9958,7 @@
       </c>
     </row>
     <row r="405" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G405" s="73"/>
+      <c r="G405" s="70"/>
       <c r="H405" s="24"/>
       <c r="I405" s="34"/>
       <c r="J405" s="34"/>
@@ -9974,7 +9977,7 @@
       </c>
     </row>
     <row r="406" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G406" s="73"/>
+      <c r="G406" s="70"/>
       <c r="H406" s="24"/>
       <c r="I406" s="34"/>
       <c r="J406" s="34"/>
@@ -9993,7 +9996,7 @@
       </c>
     </row>
     <row r="407" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G407" s="73"/>
+      <c r="G407" s="70"/>
       <c r="H407" s="24"/>
       <c r="I407" s="34"/>
       <c r="J407" s="34"/>
@@ -10012,7 +10015,7 @@
       </c>
     </row>
     <row r="408" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G408" s="73"/>
+      <c r="G408" s="70"/>
       <c r="H408" s="24"/>
       <c r="I408" s="34"/>
       <c r="J408" s="34"/>
@@ -10031,7 +10034,7 @@
       </c>
     </row>
     <row r="409" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G409" s="73"/>
+      <c r="G409" s="70"/>
       <c r="H409" s="24"/>
       <c r="I409" s="34"/>
       <c r="J409" s="34"/>
@@ -10050,7 +10053,7 @@
       </c>
     </row>
     <row r="410" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G410" s="73"/>
+      <c r="G410" s="70"/>
       <c r="H410" s="24"/>
       <c r="I410" s="34"/>
       <c r="J410" s="34"/>
@@ -10069,7 +10072,7 @@
       </c>
     </row>
     <row r="411" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G411" s="73"/>
+      <c r="G411" s="70"/>
       <c r="H411" s="24"/>
       <c r="I411" s="34"/>
       <c r="J411" s="34"/>
@@ -10088,7 +10091,7 @@
       </c>
     </row>
     <row r="412" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G412" s="73"/>
+      <c r="G412" s="70"/>
       <c r="H412" s="24"/>
       <c r="I412" s="34"/>
       <c r="J412" s="34"/>
@@ -10107,7 +10110,7 @@
       </c>
     </row>
     <row r="413" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G413" s="73"/>
+      <c r="G413" s="70"/>
       <c r="H413" s="24"/>
       <c r="I413" s="34"/>
       <c r="J413" s="34"/>
@@ -10126,7 +10129,7 @@
       </c>
     </row>
     <row r="414" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G414" s="73"/>
+      <c r="G414" s="70"/>
       <c r="H414" s="24"/>
       <c r="I414" s="34"/>
       <c r="J414" s="34"/>
@@ -10145,7 +10148,7 @@
       </c>
     </row>
     <row r="415" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G415" s="73"/>
+      <c r="G415" s="70"/>
       <c r="H415" s="24"/>
       <c r="I415" s="34"/>
       <c r="J415" s="34"/>
@@ -10164,7 +10167,7 @@
       </c>
     </row>
     <row r="416" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G416" s="73"/>
+      <c r="G416" s="70"/>
       <c r="H416" s="24"/>
       <c r="I416" s="34"/>
       <c r="J416" s="34"/>
@@ -10183,7 +10186,7 @@
       </c>
     </row>
     <row r="417" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G417" s="73"/>
+      <c r="G417" s="70"/>
       <c r="H417" s="24"/>
       <c r="I417" s="34"/>
       <c r="J417" s="34"/>
@@ -10202,7 +10205,7 @@
       </c>
     </row>
     <row r="418" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G418" s="73"/>
+      <c r="G418" s="70"/>
       <c r="H418" s="24"/>
       <c r="I418" s="34"/>
       <c r="J418" s="34"/>
@@ -10221,7 +10224,7 @@
       </c>
     </row>
     <row r="419" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G419" s="73"/>
+      <c r="G419" s="70"/>
       <c r="H419" s="24"/>
       <c r="I419" s="34"/>
       <c r="J419" s="34"/>
@@ -10240,7 +10243,7 @@
       </c>
     </row>
     <row r="420" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G420" s="73"/>
+      <c r="G420" s="70"/>
       <c r="H420" s="24"/>
       <c r="I420" s="34"/>
       <c r="J420" s="34"/>
@@ -10259,7 +10262,7 @@
       </c>
     </row>
     <row r="421" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G421" s="73"/>
+      <c r="G421" s="70"/>
       <c r="H421" s="24"/>
       <c r="I421" s="34"/>
       <c r="J421" s="34"/>
@@ -10278,7 +10281,7 @@
       </c>
     </row>
     <row r="422" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G422" s="73"/>
+      <c r="G422" s="70"/>
       <c r="H422" s="24"/>
       <c r="I422" s="34"/>
       <c r="J422" s="34"/>
@@ -10297,7 +10300,7 @@
       </c>
     </row>
     <row r="423" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G423" s="73"/>
+      <c r="G423" s="70"/>
       <c r="H423" s="24"/>
       <c r="I423" s="34"/>
       <c r="J423" s="34"/>
@@ -10316,7 +10319,7 @@
       </c>
     </row>
     <row r="424" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G424" s="73"/>
+      <c r="G424" s="70"/>
       <c r="H424" s="24"/>
       <c r="I424" s="34"/>
       <c r="J424" s="34"/>
@@ -10335,7 +10338,7 @@
       </c>
     </row>
     <row r="425" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G425" s="73"/>
+      <c r="G425" s="70"/>
       <c r="H425" s="24"/>
       <c r="I425" s="34"/>
       <c r="J425" s="34"/>
@@ -10354,7 +10357,7 @@
       </c>
     </row>
     <row r="426" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G426" s="73"/>
+      <c r="G426" s="70"/>
       <c r="H426" s="24"/>
       <c r="I426" s="34"/>
       <c r="J426" s="34"/>
@@ -10373,7 +10376,7 @@
       </c>
     </row>
     <row r="427" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G427" s="73"/>
+      <c r="G427" s="70"/>
       <c r="H427" s="24"/>
       <c r="I427" s="34"/>
       <c r="J427" s="34"/>
@@ -10392,7 +10395,7 @@
       </c>
     </row>
     <row r="428" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G428" s="73"/>
+      <c r="G428" s="70"/>
       <c r="H428" s="24"/>
       <c r="I428" s="34"/>
       <c r="J428" s="34"/>
@@ -10411,7 +10414,7 @@
       </c>
     </row>
     <row r="429" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G429" s="73"/>
+      <c r="G429" s="70"/>
       <c r="H429" s="24"/>
       <c r="I429" s="34"/>
       <c r="J429" s="34"/>
@@ -10430,7 +10433,7 @@
       </c>
     </row>
     <row r="430" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G430" s="73"/>
+      <c r="G430" s="70"/>
       <c r="H430" s="24"/>
       <c r="I430" s="34"/>
       <c r="J430" s="34"/>
@@ -10449,7 +10452,7 @@
       </c>
     </row>
     <row r="431" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G431" s="73"/>
+      <c r="G431" s="70"/>
       <c r="H431" s="24"/>
       <c r="I431" s="34"/>
       <c r="J431" s="34"/>
@@ -10468,7 +10471,7 @@
       </c>
     </row>
     <row r="432" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G432" s="73"/>
+      <c r="G432" s="70"/>
       <c r="H432" s="24"/>
       <c r="I432" s="34"/>
       <c r="J432" s="34"/>
@@ -10487,7 +10490,7 @@
       </c>
     </row>
     <row r="433" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G433" s="73"/>
+      <c r="G433" s="70"/>
       <c r="H433" s="24"/>
       <c r="I433" s="34"/>
       <c r="J433" s="34"/>
@@ -10506,7 +10509,7 @@
       </c>
     </row>
     <row r="434" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G434" s="73"/>
+      <c r="G434" s="70"/>
       <c r="H434" s="24"/>
       <c r="I434" s="34"/>
       <c r="J434" s="34"/>
@@ -10525,7 +10528,7 @@
       </c>
     </row>
     <row r="435" spans="7:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G435" s="74"/>
+      <c r="G435" s="71"/>
       <c r="H435" s="36"/>
       <c r="I435" s="37"/>
       <c r="J435" s="37"/>
@@ -10564,19 +10567,19 @@
     </row>
     <row r="438" spans="7:18" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="439" spans="7:18" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="H439" s="69" t="s">
+      <c r="H439" s="72" t="s">
         <v>55</v>
       </c>
-      <c r="I439" s="70"/>
-      <c r="J439" s="70"/>
-      <c r="K439" s="70"/>
-      <c r="L439" s="70"/>
-      <c r="M439" s="70"/>
-      <c r="N439" s="70"/>
-      <c r="O439" s="71"/>
+      <c r="I439" s="73"/>
+      <c r="J439" s="73"/>
+      <c r="K439" s="73"/>
+      <c r="L439" s="73"/>
+      <c r="M439" s="73"/>
+      <c r="N439" s="73"/>
+      <c r="O439" s="74"/>
     </row>
     <row r="440" spans="7:18" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="G440" s="72" t="s">
+      <c r="G440" s="69" t="s">
         <v>56</v>
       </c>
       <c r="H440" s="56" t="s">
@@ -10605,7 +10608,7 @@
       </c>
     </row>
     <row r="441" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G441" s="73"/>
+      <c r="G441" s="70"/>
       <c r="H441" s="53"/>
       <c r="I441" s="54"/>
       <c r="J441" s="54"/>
@@ -10624,7 +10627,7 @@
       </c>
     </row>
     <row r="442" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G442" s="73"/>
+      <c r="G442" s="70"/>
       <c r="H442" s="53"/>
       <c r="I442" s="34"/>
       <c r="J442" s="34"/>
@@ -10643,7 +10646,7 @@
       </c>
     </row>
     <row r="443" spans="7:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G443" s="73"/>
+      <c r="G443" s="70"/>
       <c r="H443" s="53"/>
       <c r="I443" s="34"/>
       <c r="J443" s="34"/>
@@ -10662,7 +10665,7 @@
       </c>
     </row>
     <row r="444" spans="7:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G444" s="73"/>
+      <c r="G444" s="70"/>
       <c r="H444" s="53"/>
       <c r="I444" s="34"/>
       <c r="J444" s="34"/>
@@ -10679,13 +10682,13 @@
         <f t="shared" si="19"/>
         <v>1423</v>
       </c>
-      <c r="Q444" s="75" t="s">
+      <c r="Q444" s="79" t="s">
         <v>70</v>
       </c>
-      <c r="R444" s="76"/>
+      <c r="R444" s="80"/>
     </row>
     <row r="445" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G445" s="73"/>
+      <c r="G445" s="70"/>
       <c r="H445" s="53"/>
       <c r="I445" s="34"/>
       <c r="J445" s="34"/>
@@ -10708,7 +10711,7 @@
       <c r="R445" s="62"/>
     </row>
     <row r="446" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G446" s="73"/>
+      <c r="G446" s="70"/>
       <c r="H446" s="53"/>
       <c r="I446" s="34"/>
       <c r="J446" s="34"/>
@@ -10731,7 +10734,7 @@
       <c r="R446" s="64"/>
     </row>
     <row r="447" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G447" s="73"/>
+      <c r="G447" s="70"/>
       <c r="H447" s="53"/>
       <c r="I447" s="34"/>
       <c r="J447" s="34"/>
@@ -10754,7 +10757,7 @@
       <c r="R447" s="64"/>
     </row>
     <row r="448" spans="7:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G448" s="73"/>
+      <c r="G448" s="70"/>
       <c r="H448" s="53"/>
       <c r="I448" s="34"/>
       <c r="J448" s="34"/>
@@ -10777,7 +10780,7 @@
       <c r="R448" s="66"/>
     </row>
     <row r="449" spans="7:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G449" s="73"/>
+      <c r="G449" s="70"/>
       <c r="H449" s="43"/>
       <c r="I449" s="34"/>
       <c r="J449" s="34"/>
@@ -10803,7 +10806,7 @@
       </c>
     </row>
     <row r="450" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G450" s="73"/>
+      <c r="G450" s="70"/>
       <c r="H450" s="43"/>
       <c r="I450" s="34"/>
       <c r="J450" s="34"/>
@@ -10822,7 +10825,7 @@
       </c>
     </row>
     <row r="451" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G451" s="73"/>
+      <c r="G451" s="70"/>
       <c r="H451" s="43"/>
       <c r="I451" s="34"/>
       <c r="J451" s="34"/>
@@ -10841,7 +10844,7 @@
       </c>
     </row>
     <row r="452" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G452" s="73"/>
+      <c r="G452" s="70"/>
       <c r="H452" s="43"/>
       <c r="I452" s="34"/>
       <c r="J452" s="34"/>
@@ -10860,7 +10863,7 @@
       </c>
     </row>
     <row r="453" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G453" s="73"/>
+      <c r="G453" s="70"/>
       <c r="H453" s="43"/>
       <c r="I453" s="34"/>
       <c r="J453" s="34"/>
@@ -10879,7 +10882,7 @@
       </c>
     </row>
     <row r="454" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G454" s="73"/>
+      <c r="G454" s="70"/>
       <c r="H454" s="43"/>
       <c r="I454" s="34"/>
       <c r="J454" s="34"/>
@@ -10898,7 +10901,7 @@
       </c>
     </row>
     <row r="455" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G455" s="73"/>
+      <c r="G455" s="70"/>
       <c r="H455" s="43"/>
       <c r="I455" s="34"/>
       <c r="J455" s="34"/>
@@ -10917,7 +10920,7 @@
       </c>
     </row>
     <row r="456" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G456" s="73"/>
+      <c r="G456" s="70"/>
       <c r="H456" s="43"/>
       <c r="I456" s="34"/>
       <c r="J456" s="34"/>
@@ -10936,7 +10939,7 @@
       </c>
     </row>
     <row r="457" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G457" s="73"/>
+      <c r="G457" s="70"/>
       <c r="H457" s="43"/>
       <c r="I457" s="34"/>
       <c r="J457" s="34"/>
@@ -10955,7 +10958,7 @@
       </c>
     </row>
     <row r="458" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G458" s="73"/>
+      <c r="G458" s="70"/>
       <c r="H458" s="24"/>
       <c r="I458" s="34"/>
       <c r="J458" s="34"/>
@@ -10974,7 +10977,7 @@
       </c>
     </row>
     <row r="459" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G459" s="73"/>
+      <c r="G459" s="70"/>
       <c r="H459" s="24"/>
       <c r="I459" s="34"/>
       <c r="J459" s="34"/>
@@ -10993,7 +10996,7 @@
       </c>
     </row>
     <row r="460" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G460" s="73"/>
+      <c r="G460" s="70"/>
       <c r="H460" s="24"/>
       <c r="I460" s="34"/>
       <c r="J460" s="34"/>
@@ -11012,7 +11015,7 @@
       </c>
     </row>
     <row r="461" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G461" s="73"/>
+      <c r="G461" s="70"/>
       <c r="H461" s="24"/>
       <c r="I461" s="34"/>
       <c r="J461" s="34"/>
@@ -11031,7 +11034,7 @@
       </c>
     </row>
     <row r="462" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G462" s="73"/>
+      <c r="G462" s="70"/>
       <c r="H462" s="24"/>
       <c r="I462" s="34"/>
       <c r="J462" s="34"/>
@@ -11050,7 +11053,7 @@
       </c>
     </row>
     <row r="463" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G463" s="73"/>
+      <c r="G463" s="70"/>
       <c r="H463" s="24"/>
       <c r="I463" s="34"/>
       <c r="J463" s="34"/>
@@ -11069,7 +11072,7 @@
       </c>
     </row>
     <row r="464" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G464" s="73"/>
+      <c r="G464" s="70"/>
       <c r="H464" s="24"/>
       <c r="I464" s="34"/>
       <c r="J464" s="34"/>
@@ -11088,7 +11091,7 @@
       </c>
     </row>
     <row r="465" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G465" s="73"/>
+      <c r="G465" s="70"/>
       <c r="H465" s="24"/>
       <c r="I465" s="34"/>
       <c r="J465" s="34"/>
@@ -11107,7 +11110,7 @@
       </c>
     </row>
     <row r="466" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G466" s="73"/>
+      <c r="G466" s="70"/>
       <c r="H466" s="24"/>
       <c r="I466" s="34"/>
       <c r="J466" s="34"/>
@@ -11126,7 +11129,7 @@
       </c>
     </row>
     <row r="467" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G467" s="73"/>
+      <c r="G467" s="70"/>
       <c r="H467" s="24"/>
       <c r="I467" s="34"/>
       <c r="J467" s="34"/>
@@ -11145,7 +11148,7 @@
       </c>
     </row>
     <row r="468" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G468" s="73"/>
+      <c r="G468" s="70"/>
       <c r="H468" s="24"/>
       <c r="I468" s="34"/>
       <c r="J468" s="34"/>
@@ -11164,7 +11167,7 @@
       </c>
     </row>
     <row r="469" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G469" s="73"/>
+      <c r="G469" s="70"/>
       <c r="H469" s="24"/>
       <c r="I469" s="34"/>
       <c r="J469" s="34"/>
@@ -11183,7 +11186,7 @@
       </c>
     </row>
     <row r="470" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G470" s="73"/>
+      <c r="G470" s="70"/>
       <c r="H470" s="24"/>
       <c r="I470" s="34"/>
       <c r="J470" s="34"/>
@@ -11202,7 +11205,7 @@
       </c>
     </row>
     <row r="471" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G471" s="73"/>
+      <c r="G471" s="70"/>
       <c r="H471" s="24"/>
       <c r="I471" s="34"/>
       <c r="J471" s="34"/>
@@ -11221,7 +11224,7 @@
       </c>
     </row>
     <row r="472" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G472" s="73"/>
+      <c r="G472" s="70"/>
       <c r="H472" s="24"/>
       <c r="I472" s="34"/>
       <c r="J472" s="34"/>
@@ -11240,7 +11243,7 @@
       </c>
     </row>
     <row r="473" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G473" s="73"/>
+      <c r="G473" s="70"/>
       <c r="H473" s="24"/>
       <c r="I473" s="34"/>
       <c r="J473" s="34"/>
@@ -11259,7 +11262,7 @@
       </c>
     </row>
     <row r="474" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G474" s="73"/>
+      <c r="G474" s="70"/>
       <c r="H474" s="24"/>
       <c r="I474" s="34"/>
       <c r="J474" s="34"/>
@@ -11278,7 +11281,7 @@
       </c>
     </row>
     <row r="475" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G475" s="73"/>
+      <c r="G475" s="70"/>
       <c r="H475" s="24"/>
       <c r="I475" s="34"/>
       <c r="J475" s="34"/>
@@ -11297,7 +11300,7 @@
       </c>
     </row>
     <row r="476" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G476" s="73"/>
+      <c r="G476" s="70"/>
       <c r="H476" s="24"/>
       <c r="I476" s="34"/>
       <c r="J476" s="34"/>
@@ -11316,7 +11319,7 @@
       </c>
     </row>
     <row r="477" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G477" s="73"/>
+      <c r="G477" s="70"/>
       <c r="H477" s="24"/>
       <c r="I477" s="34"/>
       <c r="J477" s="34"/>
@@ -11335,7 +11338,7 @@
       </c>
     </row>
     <row r="478" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G478" s="73"/>
+      <c r="G478" s="70"/>
       <c r="H478" s="24"/>
       <c r="I478" s="34"/>
       <c r="J478" s="34"/>
@@ -11354,7 +11357,7 @@
       </c>
     </row>
     <row r="479" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G479" s="73"/>
+      <c r="G479" s="70"/>
       <c r="H479" s="24"/>
       <c r="I479" s="34"/>
       <c r="J479" s="34"/>
@@ -11373,7 +11376,7 @@
       </c>
     </row>
     <row r="480" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G480" s="73"/>
+      <c r="G480" s="70"/>
       <c r="H480" s="24"/>
       <c r="I480" s="34"/>
       <c r="J480" s="34"/>
@@ -11392,7 +11395,7 @@
       </c>
     </row>
     <row r="481" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G481" s="73"/>
+      <c r="G481" s="70"/>
       <c r="H481" s="24"/>
       <c r="I481" s="34"/>
       <c r="J481" s="34"/>
@@ -11411,7 +11414,7 @@
       </c>
     </row>
     <row r="482" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G482" s="73"/>
+      <c r="G482" s="70"/>
       <c r="H482" s="24"/>
       <c r="I482" s="34"/>
       <c r="J482" s="34"/>
@@ -11430,7 +11433,7 @@
       </c>
     </row>
     <row r="483" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G483" s="73"/>
+      <c r="G483" s="70"/>
       <c r="H483" s="24"/>
       <c r="I483" s="34"/>
       <c r="J483" s="34"/>
@@ -11449,7 +11452,7 @@
       </c>
     </row>
     <row r="484" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G484" s="73"/>
+      <c r="G484" s="70"/>
       <c r="H484" s="24"/>
       <c r="I484" s="34"/>
       <c r="J484" s="34"/>
@@ -11468,7 +11471,7 @@
       </c>
     </row>
     <row r="485" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G485" s="73"/>
+      <c r="G485" s="70"/>
       <c r="H485" s="24"/>
       <c r="I485" s="34"/>
       <c r="J485" s="34"/>
@@ -11487,7 +11490,7 @@
       </c>
     </row>
     <row r="486" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G486" s="73"/>
+      <c r="G486" s="70"/>
       <c r="H486" s="24"/>
       <c r="I486" s="34"/>
       <c r="J486" s="34"/>
@@ -11506,7 +11509,7 @@
       </c>
     </row>
     <row r="487" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G487" s="73"/>
+      <c r="G487" s="70"/>
       <c r="H487" s="24"/>
       <c r="I487" s="34"/>
       <c r="J487" s="34"/>
@@ -11525,7 +11528,7 @@
       </c>
     </row>
     <row r="488" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G488" s="73"/>
+      <c r="G488" s="70"/>
       <c r="H488" s="24"/>
       <c r="I488" s="34"/>
       <c r="J488" s="34"/>
@@ -11544,7 +11547,7 @@
       </c>
     </row>
     <row r="489" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G489" s="73"/>
+      <c r="G489" s="70"/>
       <c r="H489" s="24"/>
       <c r="I489" s="34"/>
       <c r="J489" s="34"/>
@@ -11563,7 +11566,7 @@
       </c>
     </row>
     <row r="490" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G490" s="73"/>
+      <c r="G490" s="70"/>
       <c r="H490" s="24"/>
       <c r="I490" s="34"/>
       <c r="J490" s="34"/>
@@ -11582,7 +11585,7 @@
       </c>
     </row>
     <row r="491" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G491" s="73"/>
+      <c r="G491" s="70"/>
       <c r="H491" s="24"/>
       <c r="I491" s="34"/>
       <c r="J491" s="34"/>
@@ -11601,7 +11604,7 @@
       </c>
     </row>
     <row r="492" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G492" s="73"/>
+      <c r="G492" s="70"/>
       <c r="H492" s="24"/>
       <c r="I492" s="34"/>
       <c r="J492" s="34"/>
@@ -11620,7 +11623,7 @@
       </c>
     </row>
     <row r="493" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G493" s="73"/>
+      <c r="G493" s="70"/>
       <c r="H493" s="24"/>
       <c r="I493" s="34"/>
       <c r="J493" s="34"/>
@@ -11639,7 +11642,7 @@
       </c>
     </row>
     <row r="494" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G494" s="73"/>
+      <c r="G494" s="70"/>
       <c r="H494" s="24"/>
       <c r="I494" s="34"/>
       <c r="J494" s="34"/>
@@ -11658,7 +11661,7 @@
       </c>
     </row>
     <row r="495" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G495" s="73"/>
+      <c r="G495" s="70"/>
       <c r="H495" s="24"/>
       <c r="I495" s="34"/>
       <c r="J495" s="34"/>
@@ -11677,7 +11680,7 @@
       </c>
     </row>
     <row r="496" spans="7:15" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G496" s="74"/>
+      <c r="G496" s="71"/>
       <c r="H496" s="36"/>
       <c r="I496" s="37"/>
       <c r="J496" s="37"/>
@@ -11716,19 +11719,19 @@
     </row>
     <row r="499" spans="7:18" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="500" spans="7:18" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="H500" s="69" t="s">
+      <c r="H500" s="72" t="s">
         <v>57</v>
       </c>
-      <c r="I500" s="70"/>
-      <c r="J500" s="70"/>
-      <c r="K500" s="70"/>
-      <c r="L500" s="70"/>
-      <c r="M500" s="70"/>
-      <c r="N500" s="70"/>
-      <c r="O500" s="71"/>
+      <c r="I500" s="73"/>
+      <c r="J500" s="73"/>
+      <c r="K500" s="73"/>
+      <c r="L500" s="73"/>
+      <c r="M500" s="73"/>
+      <c r="N500" s="73"/>
+      <c r="O500" s="74"/>
     </row>
     <row r="501" spans="7:18" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="G501" s="72" t="s">
+      <c r="G501" s="69" t="s">
         <v>58</v>
       </c>
       <c r="H501" s="56" t="s">
@@ -11757,7 +11760,7 @@
       </c>
     </row>
     <row r="502" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G502" s="73"/>
+      <c r="G502" s="70"/>
       <c r="H502" s="53"/>
       <c r="I502" s="54"/>
       <c r="J502" s="54"/>
@@ -11776,7 +11779,7 @@
       </c>
     </row>
     <row r="503" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G503" s="73"/>
+      <c r="G503" s="70"/>
       <c r="H503" s="53"/>
       <c r="I503" s="34"/>
       <c r="J503" s="34"/>
@@ -11795,7 +11798,7 @@
       </c>
     </row>
     <row r="504" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G504" s="73"/>
+      <c r="G504" s="70"/>
       <c r="H504" s="53"/>
       <c r="I504" s="34"/>
       <c r="J504" s="34"/>
@@ -11814,7 +11817,7 @@
       </c>
     </row>
     <row r="505" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G505" s="73"/>
+      <c r="G505" s="70"/>
       <c r="H505" s="53"/>
       <c r="I505" s="34"/>
       <c r="J505" s="34"/>
@@ -11833,7 +11836,7 @@
       </c>
     </row>
     <row r="506" spans="7:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G506" s="73"/>
+      <c r="G506" s="70"/>
       <c r="H506" s="53"/>
       <c r="I506" s="34"/>
       <c r="J506" s="34"/>
@@ -11852,7 +11855,7 @@
       </c>
     </row>
     <row r="507" spans="7:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G507" s="73"/>
+      <c r="G507" s="70"/>
       <c r="H507" s="53"/>
       <c r="I507" s="34"/>
       <c r="J507" s="34"/>
@@ -11869,13 +11872,13 @@
         <f t="shared" si="21"/>
         <v>1423</v>
       </c>
-      <c r="Q507" s="75" t="s">
+      <c r="Q507" s="79" t="s">
         <v>71</v>
       </c>
-      <c r="R507" s="76"/>
+      <c r="R507" s="80"/>
     </row>
     <row r="508" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G508" s="73"/>
+      <c r="G508" s="70"/>
       <c r="H508" s="53"/>
       <c r="I508" s="34"/>
       <c r="J508" s="34"/>
@@ -11898,7 +11901,7 @@
       <c r="R508" s="62"/>
     </row>
     <row r="509" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G509" s="73"/>
+      <c r="G509" s="70"/>
       <c r="H509" s="53"/>
       <c r="I509" s="34"/>
       <c r="J509" s="34"/>
@@ -11921,7 +11924,7 @@
       <c r="R509" s="64"/>
     </row>
     <row r="510" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G510" s="73"/>
+      <c r="G510" s="70"/>
       <c r="H510" s="43"/>
       <c r="I510" s="34"/>
       <c r="J510" s="34"/>
@@ -11944,7 +11947,7 @@
       <c r="R510" s="64"/>
     </row>
     <row r="511" spans="7:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G511" s="73"/>
+      <c r="G511" s="70"/>
       <c r="H511" s="43"/>
       <c r="I511" s="34"/>
       <c r="J511" s="34"/>
@@ -11967,7 +11970,7 @@
       <c r="R511" s="66"/>
     </row>
     <row r="512" spans="7:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G512" s="73"/>
+      <c r="G512" s="70"/>
       <c r="H512" s="43"/>
       <c r="I512" s="34"/>
       <c r="J512" s="34"/>
@@ -11993,7 +11996,7 @@
       </c>
     </row>
     <row r="513" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G513" s="73"/>
+      <c r="G513" s="70"/>
       <c r="H513" s="43"/>
       <c r="I513" s="34"/>
       <c r="J513" s="34"/>
@@ -12012,7 +12015,7 @@
       </c>
     </row>
     <row r="514" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G514" s="73"/>
+      <c r="G514" s="70"/>
       <c r="H514" s="43"/>
       <c r="I514" s="34"/>
       <c r="J514" s="34"/>
@@ -12031,7 +12034,7 @@
       </c>
     </row>
     <row r="515" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G515" s="73"/>
+      <c r="G515" s="70"/>
       <c r="H515" s="43"/>
       <c r="I515" s="34"/>
       <c r="J515" s="34"/>
@@ -12050,7 +12053,7 @@
       </c>
     </row>
     <row r="516" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G516" s="73"/>
+      <c r="G516" s="70"/>
       <c r="H516" s="43"/>
       <c r="I516" s="34"/>
       <c r="J516" s="34"/>
@@ -12069,7 +12072,7 @@
       </c>
     </row>
     <row r="517" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G517" s="73"/>
+      <c r="G517" s="70"/>
       <c r="H517" s="43"/>
       <c r="I517" s="34"/>
       <c r="J517" s="34"/>
@@ -12088,7 +12091,7 @@
       </c>
     </row>
     <row r="518" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G518" s="73"/>
+      <c r="G518" s="70"/>
       <c r="H518" s="43"/>
       <c r="I518" s="34"/>
       <c r="J518" s="34"/>
@@ -12107,7 +12110,7 @@
       </c>
     </row>
     <row r="519" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G519" s="73"/>
+      <c r="G519" s="70"/>
       <c r="H519" s="24"/>
       <c r="I519" s="34"/>
       <c r="J519" s="34"/>
@@ -12126,7 +12129,7 @@
       </c>
     </row>
     <row r="520" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G520" s="73"/>
+      <c r="G520" s="70"/>
       <c r="H520" s="24"/>
       <c r="I520" s="34"/>
       <c r="J520" s="34"/>
@@ -12145,7 +12148,7 @@
       </c>
     </row>
     <row r="521" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G521" s="73"/>
+      <c r="G521" s="70"/>
       <c r="H521" s="24"/>
       <c r="I521" s="34"/>
       <c r="J521" s="34"/>
@@ -12164,7 +12167,7 @@
       </c>
     </row>
     <row r="522" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G522" s="73"/>
+      <c r="G522" s="70"/>
       <c r="H522" s="24"/>
       <c r="I522" s="34"/>
       <c r="J522" s="34"/>
@@ -12183,7 +12186,7 @@
       </c>
     </row>
     <row r="523" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G523" s="73"/>
+      <c r="G523" s="70"/>
       <c r="H523" s="24"/>
       <c r="I523" s="34"/>
       <c r="J523" s="34"/>
@@ -12202,7 +12205,7 @@
       </c>
     </row>
     <row r="524" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G524" s="73"/>
+      <c r="G524" s="70"/>
       <c r="H524" s="24"/>
       <c r="I524" s="34"/>
       <c r="J524" s="34"/>
@@ -12221,7 +12224,7 @@
       </c>
     </row>
     <row r="525" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G525" s="73"/>
+      <c r="G525" s="70"/>
       <c r="H525" s="24"/>
       <c r="I525" s="34"/>
       <c r="J525" s="34"/>
@@ -12240,7 +12243,7 @@
       </c>
     </row>
     <row r="526" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G526" s="73"/>
+      <c r="G526" s="70"/>
       <c r="H526" s="24"/>
       <c r="I526" s="34"/>
       <c r="J526" s="34"/>
@@ -12259,7 +12262,7 @@
       </c>
     </row>
     <row r="527" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G527" s="73"/>
+      <c r="G527" s="70"/>
       <c r="H527" s="24"/>
       <c r="I527" s="34"/>
       <c r="J527" s="34"/>
@@ -12278,7 +12281,7 @@
       </c>
     </row>
     <row r="528" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G528" s="73"/>
+      <c r="G528" s="70"/>
       <c r="H528" s="24"/>
       <c r="I528" s="34"/>
       <c r="J528" s="34"/>
@@ -12297,7 +12300,7 @@
       </c>
     </row>
     <row r="529" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G529" s="73"/>
+      <c r="G529" s="70"/>
       <c r="H529" s="24"/>
       <c r="I529" s="34"/>
       <c r="J529" s="34"/>
@@ -12316,7 +12319,7 @@
       </c>
     </row>
     <row r="530" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G530" s="73"/>
+      <c r="G530" s="70"/>
       <c r="H530" s="24"/>
       <c r="I530" s="34"/>
       <c r="J530" s="34"/>
@@ -12335,7 +12338,7 @@
       </c>
     </row>
     <row r="531" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G531" s="73"/>
+      <c r="G531" s="70"/>
       <c r="H531" s="24"/>
       <c r="I531" s="34"/>
       <c r="J531" s="34"/>
@@ -12354,7 +12357,7 @@
       </c>
     </row>
     <row r="532" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G532" s="73"/>
+      <c r="G532" s="70"/>
       <c r="H532" s="24"/>
       <c r="I532" s="34"/>
       <c r="J532" s="34"/>
@@ -12373,7 +12376,7 @@
       </c>
     </row>
     <row r="533" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G533" s="73"/>
+      <c r="G533" s="70"/>
       <c r="H533" s="24"/>
       <c r="I533" s="34"/>
       <c r="J533" s="34"/>
@@ -12392,7 +12395,7 @@
       </c>
     </row>
     <row r="534" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G534" s="73"/>
+      <c r="G534" s="70"/>
       <c r="H534" s="24"/>
       <c r="I534" s="34"/>
       <c r="J534" s="34"/>
@@ -12411,7 +12414,7 @@
       </c>
     </row>
     <row r="535" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G535" s="73"/>
+      <c r="G535" s="70"/>
       <c r="H535" s="24"/>
       <c r="I535" s="34"/>
       <c r="J535" s="34"/>
@@ -12430,7 +12433,7 @@
       </c>
     </row>
     <row r="536" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G536" s="73"/>
+      <c r="G536" s="70"/>
       <c r="H536" s="24"/>
       <c r="I536" s="34"/>
       <c r="J536" s="34"/>
@@ -12449,7 +12452,7 @@
       </c>
     </row>
     <row r="537" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G537" s="73"/>
+      <c r="G537" s="70"/>
       <c r="H537" s="24"/>
       <c r="I537" s="34"/>
       <c r="J537" s="34"/>
@@ -12468,7 +12471,7 @@
       </c>
     </row>
     <row r="538" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G538" s="73"/>
+      <c r="G538" s="70"/>
       <c r="H538" s="24"/>
       <c r="I538" s="34"/>
       <c r="J538" s="34"/>
@@ -12487,7 +12490,7 @@
       </c>
     </row>
     <row r="539" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G539" s="73"/>
+      <c r="G539" s="70"/>
       <c r="H539" s="24"/>
       <c r="I539" s="34"/>
       <c r="J539" s="34"/>
@@ -12506,7 +12509,7 @@
       </c>
     </row>
     <row r="540" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G540" s="73"/>
+      <c r="G540" s="70"/>
       <c r="H540" s="24"/>
       <c r="I540" s="34"/>
       <c r="J540" s="34"/>
@@ -12525,7 +12528,7 @@
       </c>
     </row>
     <row r="541" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G541" s="73"/>
+      <c r="G541" s="70"/>
       <c r="H541" s="24"/>
       <c r="I541" s="34"/>
       <c r="J541" s="34"/>
@@ -12544,7 +12547,7 @@
       </c>
     </row>
     <row r="542" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G542" s="73"/>
+      <c r="G542" s="70"/>
       <c r="H542" s="24"/>
       <c r="I542" s="34"/>
       <c r="J542" s="34"/>
@@ -12563,7 +12566,7 @@
       </c>
     </row>
     <row r="543" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G543" s="73"/>
+      <c r="G543" s="70"/>
       <c r="H543" s="24"/>
       <c r="I543" s="34"/>
       <c r="J543" s="34"/>
@@ -12582,7 +12585,7 @@
       </c>
     </row>
     <row r="544" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G544" s="73"/>
+      <c r="G544" s="70"/>
       <c r="H544" s="24"/>
       <c r="I544" s="34"/>
       <c r="J544" s="34"/>
@@ -12601,7 +12604,7 @@
       </c>
     </row>
     <row r="545" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G545" s="73"/>
+      <c r="G545" s="70"/>
       <c r="H545" s="24"/>
       <c r="I545" s="34"/>
       <c r="J545" s="34"/>
@@ -12620,7 +12623,7 @@
       </c>
     </row>
     <row r="546" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G546" s="73"/>
+      <c r="G546" s="70"/>
       <c r="H546" s="24"/>
       <c r="I546" s="34"/>
       <c r="J546" s="34"/>
@@ -12639,7 +12642,7 @@
       </c>
     </row>
     <row r="547" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G547" s="73"/>
+      <c r="G547" s="70"/>
       <c r="H547" s="24"/>
       <c r="I547" s="34"/>
       <c r="J547" s="34"/>
@@ -12658,7 +12661,7 @@
       </c>
     </row>
     <row r="548" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G548" s="73"/>
+      <c r="G548" s="70"/>
       <c r="H548" s="24"/>
       <c r="I548" s="34"/>
       <c r="J548" s="34"/>
@@ -12677,7 +12680,7 @@
       </c>
     </row>
     <row r="549" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G549" s="73"/>
+      <c r="G549" s="70"/>
       <c r="H549" s="24"/>
       <c r="I549" s="34"/>
       <c r="J549" s="34"/>
@@ -12696,7 +12699,7 @@
       </c>
     </row>
     <row r="550" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G550" s="73"/>
+      <c r="G550" s="70"/>
       <c r="H550" s="24"/>
       <c r="I550" s="34"/>
       <c r="J550" s="34"/>
@@ -12715,7 +12718,7 @@
       </c>
     </row>
     <row r="551" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G551" s="73"/>
+      <c r="G551" s="70"/>
       <c r="H551" s="24"/>
       <c r="I551" s="34"/>
       <c r="J551" s="34"/>
@@ -12734,7 +12737,7 @@
       </c>
     </row>
     <row r="552" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G552" s="73"/>
+      <c r="G552" s="70"/>
       <c r="H552" s="24"/>
       <c r="I552" s="34"/>
       <c r="J552" s="34"/>
@@ -12753,7 +12756,7 @@
       </c>
     </row>
     <row r="553" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G553" s="73"/>
+      <c r="G553" s="70"/>
       <c r="H553" s="24"/>
       <c r="I553" s="34"/>
       <c r="J553" s="34"/>
@@ -12772,7 +12775,7 @@
       </c>
     </row>
     <row r="554" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G554" s="73"/>
+      <c r="G554" s="70"/>
       <c r="H554" s="24"/>
       <c r="I554" s="34"/>
       <c r="J554" s="34"/>
@@ -12791,7 +12794,7 @@
       </c>
     </row>
     <row r="555" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G555" s="73"/>
+      <c r="G555" s="70"/>
       <c r="H555" s="24"/>
       <c r="I555" s="34"/>
       <c r="J555" s="34"/>
@@ -12810,7 +12813,7 @@
       </c>
     </row>
     <row r="556" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G556" s="73"/>
+      <c r="G556" s="70"/>
       <c r="H556" s="24"/>
       <c r="I556" s="34"/>
       <c r="J556" s="34"/>
@@ -12829,7 +12832,7 @@
       </c>
     </row>
     <row r="557" spans="7:15" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G557" s="74"/>
+      <c r="G557" s="71"/>
       <c r="H557" s="36"/>
       <c r="I557" s="37"/>
       <c r="J557" s="37"/>
@@ -12868,19 +12871,19 @@
     </row>
     <row r="560" spans="7:15" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="561" spans="7:18" ht="30.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="H561" s="69" t="s">
+      <c r="H561" s="72" t="s">
         <v>59</v>
       </c>
-      <c r="I561" s="70"/>
-      <c r="J561" s="70"/>
-      <c r="K561" s="70"/>
-      <c r="L561" s="70"/>
-      <c r="M561" s="70"/>
-      <c r="N561" s="70"/>
-      <c r="O561" s="71"/>
+      <c r="I561" s="73"/>
+      <c r="J561" s="73"/>
+      <c r="K561" s="73"/>
+      <c r="L561" s="73"/>
+      <c r="M561" s="73"/>
+      <c r="N561" s="73"/>
+      <c r="O561" s="74"/>
     </row>
     <row r="562" spans="7:18" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="G562" s="72" t="s">
+      <c r="G562" s="69" t="s">
         <v>60</v>
       </c>
       <c r="H562" s="56" t="s">
@@ -12909,7 +12912,7 @@
       </c>
     </row>
     <row r="563" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G563" s="73"/>
+      <c r="G563" s="70"/>
       <c r="H563" s="53"/>
       <c r="I563" s="54"/>
       <c r="J563" s="54"/>
@@ -12928,7 +12931,7 @@
       </c>
     </row>
     <row r="564" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G564" s="73"/>
+      <c r="G564" s="70"/>
       <c r="H564" s="53"/>
       <c r="I564" s="34"/>
       <c r="J564" s="34"/>
@@ -12947,7 +12950,7 @@
       </c>
     </row>
     <row r="565" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G565" s="73"/>
+      <c r="G565" s="70"/>
       <c r="H565" s="53"/>
       <c r="I565" s="34"/>
       <c r="J565" s="34"/>
@@ -12966,7 +12969,7 @@
       </c>
     </row>
     <row r="566" spans="7:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G566" s="73"/>
+      <c r="G566" s="70"/>
       <c r="H566" s="53"/>
       <c r="I566" s="34"/>
       <c r="J566" s="34"/>
@@ -12985,7 +12988,7 @@
       </c>
     </row>
     <row r="567" spans="7:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G567" s="73"/>
+      <c r="G567" s="70"/>
       <c r="H567" s="53"/>
       <c r="I567" s="34"/>
       <c r="J567" s="34"/>
@@ -13002,13 +13005,13 @@
         <f t="shared" si="23"/>
         <v>1423</v>
       </c>
-      <c r="Q567" s="75" t="s">
+      <c r="Q567" s="79" t="s">
         <v>72</v>
       </c>
-      <c r="R567" s="76"/>
+      <c r="R567" s="80"/>
     </row>
     <row r="568" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G568" s="73"/>
+      <c r="G568" s="70"/>
       <c r="H568" s="53"/>
       <c r="I568" s="34"/>
       <c r="J568" s="34"/>
@@ -13031,7 +13034,7 @@
       <c r="R568" s="62"/>
     </row>
     <row r="569" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G569" s="73"/>
+      <c r="G569" s="70"/>
       <c r="H569" s="53"/>
       <c r="I569" s="34"/>
       <c r="J569" s="34"/>
@@ -13054,7 +13057,7 @@
       <c r="R569" s="64"/>
     </row>
     <row r="570" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G570" s="73"/>
+      <c r="G570" s="70"/>
       <c r="H570" s="53"/>
       <c r="I570" s="34"/>
       <c r="J570" s="34"/>
@@ -13077,7 +13080,7 @@
       <c r="R570" s="64"/>
     </row>
     <row r="571" spans="7:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G571" s="73"/>
+      <c r="G571" s="70"/>
       <c r="H571" s="43"/>
       <c r="I571" s="34"/>
       <c r="J571" s="34"/>
@@ -13100,7 +13103,7 @@
       <c r="R571" s="66"/>
     </row>
     <row r="572" spans="7:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G572" s="73"/>
+      <c r="G572" s="70"/>
       <c r="H572" s="43"/>
       <c r="I572" s="34"/>
       <c r="J572" s="34"/>
@@ -13126,7 +13129,7 @@
       </c>
     </row>
     <row r="573" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G573" s="73"/>
+      <c r="G573" s="70"/>
       <c r="H573" s="43"/>
       <c r="I573" s="34"/>
       <c r="J573" s="34"/>
@@ -13145,7 +13148,7 @@
       </c>
     </row>
     <row r="574" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G574" s="73"/>
+      <c r="G574" s="70"/>
       <c r="H574" s="43"/>
       <c r="I574" s="34"/>
       <c r="J574" s="34"/>
@@ -13164,7 +13167,7 @@
       </c>
     </row>
     <row r="575" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G575" s="73"/>
+      <c r="G575" s="70"/>
       <c r="H575" s="43"/>
       <c r="I575" s="34"/>
       <c r="J575" s="34"/>
@@ -13183,7 +13186,7 @@
       </c>
     </row>
     <row r="576" spans="7:18" ht="16" x14ac:dyDescent="0.35">
-      <c r="G576" s="73"/>
+      <c r="G576" s="70"/>
       <c r="H576" s="43"/>
       <c r="I576" s="34"/>
       <c r="J576" s="34"/>
@@ -13202,7 +13205,7 @@
       </c>
     </row>
     <row r="577" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G577" s="73"/>
+      <c r="G577" s="70"/>
       <c r="H577" s="43"/>
       <c r="I577" s="34"/>
       <c r="J577" s="34"/>
@@ -13221,7 +13224,7 @@
       </c>
     </row>
     <row r="578" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G578" s="73"/>
+      <c r="G578" s="70"/>
       <c r="H578" s="43"/>
       <c r="I578" s="34"/>
       <c r="J578" s="34"/>
@@ -13240,7 +13243,7 @@
       </c>
     </row>
     <row r="579" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G579" s="73"/>
+      <c r="G579" s="70"/>
       <c r="H579" s="43"/>
       <c r="I579" s="34"/>
       <c r="J579" s="34"/>
@@ -13259,7 +13262,7 @@
       </c>
     </row>
     <row r="580" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G580" s="73"/>
+      <c r="G580" s="70"/>
       <c r="H580" s="24"/>
       <c r="I580" s="34"/>
       <c r="J580" s="34"/>
@@ -13278,7 +13281,7 @@
       </c>
     </row>
     <row r="581" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G581" s="73"/>
+      <c r="G581" s="70"/>
       <c r="H581" s="24"/>
       <c r="I581" s="34"/>
       <c r="J581" s="34"/>
@@ -13297,7 +13300,7 @@
       </c>
     </row>
     <row r="582" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G582" s="73"/>
+      <c r="G582" s="70"/>
       <c r="H582" s="24"/>
       <c r="I582" s="34"/>
       <c r="J582" s="34"/>
@@ -13316,7 +13319,7 @@
       </c>
     </row>
     <row r="583" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G583" s="73"/>
+      <c r="G583" s="70"/>
       <c r="H583" s="24"/>
       <c r="I583" s="34"/>
       <c r="J583" s="34"/>
@@ -13335,7 +13338,7 @@
       </c>
     </row>
     <row r="584" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G584" s="73"/>
+      <c r="G584" s="70"/>
       <c r="H584" s="24"/>
       <c r="I584" s="34"/>
       <c r="J584" s="34"/>
@@ -13354,7 +13357,7 @@
       </c>
     </row>
     <row r="585" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G585" s="73"/>
+      <c r="G585" s="70"/>
       <c r="H585" s="24"/>
       <c r="I585" s="34"/>
       <c r="J585" s="34"/>
@@ -13373,7 +13376,7 @@
       </c>
     </row>
     <row r="586" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G586" s="73"/>
+      <c r="G586" s="70"/>
       <c r="H586" s="24"/>
       <c r="I586" s="34"/>
       <c r="J586" s="34"/>
@@ -13392,7 +13395,7 @@
       </c>
     </row>
     <row r="587" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G587" s="73"/>
+      <c r="G587" s="70"/>
       <c r="H587" s="24"/>
       <c r="I587" s="34"/>
       <c r="J587" s="34"/>
@@ -13411,7 +13414,7 @@
       </c>
     </row>
     <row r="588" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G588" s="73"/>
+      <c r="G588" s="70"/>
       <c r="H588" s="24"/>
       <c r="I588" s="34"/>
       <c r="J588" s="34"/>
@@ -13430,7 +13433,7 @@
       </c>
     </row>
     <row r="589" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G589" s="73"/>
+      <c r="G589" s="70"/>
       <c r="H589" s="24"/>
       <c r="I589" s="34"/>
       <c r="J589" s="34"/>
@@ -13449,7 +13452,7 @@
       </c>
     </row>
     <row r="590" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G590" s="73"/>
+      <c r="G590" s="70"/>
       <c r="H590" s="24"/>
       <c r="I590" s="34"/>
       <c r="J590" s="34"/>
@@ -13468,7 +13471,7 @@
       </c>
     </row>
     <row r="591" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G591" s="73"/>
+      <c r="G591" s="70"/>
       <c r="H591" s="24"/>
       <c r="I591" s="34"/>
       <c r="J591" s="34"/>
@@ -13487,7 +13490,7 @@
       </c>
     </row>
     <row r="592" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G592" s="73"/>
+      <c r="G592" s="70"/>
       <c r="H592" s="24"/>
       <c r="I592" s="34"/>
       <c r="J592" s="34"/>
@@ -13506,7 +13509,7 @@
       </c>
     </row>
     <row r="593" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G593" s="73"/>
+      <c r="G593" s="70"/>
       <c r="H593" s="24"/>
       <c r="I593" s="34"/>
       <c r="J593" s="34"/>
@@ -13525,7 +13528,7 @@
       </c>
     </row>
     <row r="594" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G594" s="73"/>
+      <c r="G594" s="70"/>
       <c r="H594" s="24"/>
       <c r="I594" s="34"/>
       <c r="J594" s="34"/>
@@ -13544,7 +13547,7 @@
       </c>
     </row>
     <row r="595" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G595" s="73"/>
+      <c r="G595" s="70"/>
       <c r="H595" s="24"/>
       <c r="I595" s="34"/>
       <c r="J595" s="34"/>
@@ -13563,7 +13566,7 @@
       </c>
     </row>
     <row r="596" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G596" s="73"/>
+      <c r="G596" s="70"/>
       <c r="H596" s="24"/>
       <c r="I596" s="34"/>
       <c r="J596" s="34"/>
@@ -13582,7 +13585,7 @@
       </c>
     </row>
     <row r="597" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G597" s="73"/>
+      <c r="G597" s="70"/>
       <c r="H597" s="24"/>
       <c r="I597" s="34"/>
       <c r="J597" s="34"/>
@@ -13601,7 +13604,7 @@
       </c>
     </row>
     <row r="598" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G598" s="73"/>
+      <c r="G598" s="70"/>
       <c r="H598" s="24"/>
       <c r="I598" s="34"/>
       <c r="J598" s="34"/>
@@ -13620,7 +13623,7 @@
       </c>
     </row>
     <row r="599" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G599" s="73"/>
+      <c r="G599" s="70"/>
       <c r="H599" s="24"/>
       <c r="I599" s="34"/>
       <c r="J599" s="34"/>
@@ -13639,7 +13642,7 @@
       </c>
     </row>
     <row r="600" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G600" s="73"/>
+      <c r="G600" s="70"/>
       <c r="H600" s="24"/>
       <c r="I600" s="34"/>
       <c r="J600" s="34"/>
@@ -13658,7 +13661,7 @@
       </c>
     </row>
     <row r="601" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G601" s="73"/>
+      <c r="G601" s="70"/>
       <c r="H601" s="24"/>
       <c r="I601" s="34"/>
       <c r="J601" s="34"/>
@@ -13677,7 +13680,7 @@
       </c>
     </row>
     <row r="602" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G602" s="73"/>
+      <c r="G602" s="70"/>
       <c r="H602" s="24"/>
       <c r="I602" s="34"/>
       <c r="J602" s="34"/>
@@ -13696,7 +13699,7 @@
       </c>
     </row>
     <row r="603" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G603" s="73"/>
+      <c r="G603" s="70"/>
       <c r="H603" s="24"/>
       <c r="I603" s="34"/>
       <c r="J603" s="34"/>
@@ -13715,7 +13718,7 @@
       </c>
     </row>
     <row r="604" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G604" s="73"/>
+      <c r="G604" s="70"/>
       <c r="H604" s="24"/>
       <c r="I604" s="34"/>
       <c r="J604" s="34"/>
@@ -13734,7 +13737,7 @@
       </c>
     </row>
     <row r="605" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G605" s="73"/>
+      <c r="G605" s="70"/>
       <c r="H605" s="24"/>
       <c r="I605" s="34"/>
       <c r="J605" s="34"/>
@@ -13753,7 +13756,7 @@
       </c>
     </row>
     <row r="606" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G606" s="73"/>
+      <c r="G606" s="70"/>
       <c r="H606" s="24"/>
       <c r="I606" s="34"/>
       <c r="J606" s="34"/>
@@ -13772,7 +13775,7 @@
       </c>
     </row>
     <row r="607" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G607" s="73"/>
+      <c r="G607" s="70"/>
       <c r="H607" s="24"/>
       <c r="I607" s="34"/>
       <c r="J607" s="34"/>
@@ -13791,7 +13794,7 @@
       </c>
     </row>
     <row r="608" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G608" s="73"/>
+      <c r="G608" s="70"/>
       <c r="H608" s="24"/>
       <c r="I608" s="34"/>
       <c r="J608" s="34"/>
@@ -13810,7 +13813,7 @@
       </c>
     </row>
     <row r="609" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G609" s="73"/>
+      <c r="G609" s="70"/>
       <c r="H609" s="24"/>
       <c r="I609" s="34"/>
       <c r="J609" s="34"/>
@@ -13829,7 +13832,7 @@
       </c>
     </row>
     <row r="610" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G610" s="73"/>
+      <c r="G610" s="70"/>
       <c r="H610" s="24"/>
       <c r="I610" s="34"/>
       <c r="J610" s="34"/>
@@ -13848,7 +13851,7 @@
       </c>
     </row>
     <row r="611" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G611" s="73"/>
+      <c r="G611" s="70"/>
       <c r="H611" s="24"/>
       <c r="I611" s="34"/>
       <c r="J611" s="34"/>
@@ -13867,7 +13870,7 @@
       </c>
     </row>
     <row r="612" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G612" s="73"/>
+      <c r="G612" s="70"/>
       <c r="H612" s="24"/>
       <c r="I612" s="34"/>
       <c r="J612" s="34"/>
@@ -13886,7 +13889,7 @@
       </c>
     </row>
     <row r="613" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G613" s="73"/>
+      <c r="G613" s="70"/>
       <c r="H613" s="24"/>
       <c r="I613" s="34"/>
       <c r="J613" s="34"/>
@@ -13905,7 +13908,7 @@
       </c>
     </row>
     <row r="614" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G614" s="73"/>
+      <c r="G614" s="70"/>
       <c r="H614" s="24"/>
       <c r="I614" s="34"/>
       <c r="J614" s="34"/>
@@ -13924,7 +13927,7 @@
       </c>
     </row>
     <row r="615" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G615" s="73"/>
+      <c r="G615" s="70"/>
       <c r="H615" s="24"/>
       <c r="I615" s="34"/>
       <c r="J615" s="34"/>
@@ -13943,7 +13946,7 @@
       </c>
     </row>
     <row r="616" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G616" s="73"/>
+      <c r="G616" s="70"/>
       <c r="H616" s="24"/>
       <c r="I616" s="34"/>
       <c r="J616" s="34"/>
@@ -13962,7 +13965,7 @@
       </c>
     </row>
     <row r="617" spans="7:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="G617" s="73"/>
+      <c r="G617" s="70"/>
       <c r="H617" s="24"/>
       <c r="I617" s="34"/>
       <c r="J617" s="34"/>
@@ -13981,7 +13984,7 @@
       </c>
     </row>
     <row r="618" spans="7:15" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G618" s="74"/>
+      <c r="G618" s="71"/>
       <c r="H618" s="36"/>
       <c r="I618" s="37"/>
       <c r="J618" s="37"/>
@@ -14021,24 +14024,6 @@
   </sheetData>
   <autoFilter ref="H2:O25" xr:uid="{9790A859-5FFC-4740-9EDE-6734F2B6A5D5}"/>
   <mergeCells count="34">
-    <mergeCell ref="G134:G190"/>
-    <mergeCell ref="H133:O133"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="H1:O1"/>
-    <mergeCell ref="G2:G24"/>
-    <mergeCell ref="H89:O89"/>
-    <mergeCell ref="G90:G127"/>
-    <mergeCell ref="H28:O28"/>
-    <mergeCell ref="G29:G85"/>
-    <mergeCell ref="H378:O378"/>
-    <mergeCell ref="G379:G435"/>
-    <mergeCell ref="H439:O439"/>
-    <mergeCell ref="G440:G496"/>
-    <mergeCell ref="H195:O195"/>
-    <mergeCell ref="G196:G252"/>
-    <mergeCell ref="H256:O256"/>
-    <mergeCell ref="G257:G313"/>
-    <mergeCell ref="H317:O317"/>
     <mergeCell ref="H500:O500"/>
     <mergeCell ref="G501:G557"/>
     <mergeCell ref="H561:O561"/>
@@ -14055,6 +14040,24 @@
     <mergeCell ref="Q507:R507"/>
     <mergeCell ref="Q567:R567"/>
     <mergeCell ref="G318:G374"/>
+    <mergeCell ref="H378:O378"/>
+    <mergeCell ref="G379:G435"/>
+    <mergeCell ref="H439:O439"/>
+    <mergeCell ref="G440:G496"/>
+    <mergeCell ref="H195:O195"/>
+    <mergeCell ref="G196:G252"/>
+    <mergeCell ref="H256:O256"/>
+    <mergeCell ref="G257:G313"/>
+    <mergeCell ref="H317:O317"/>
+    <mergeCell ref="G134:G190"/>
+    <mergeCell ref="H133:O133"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="H1:O1"/>
+    <mergeCell ref="G2:G24"/>
+    <mergeCell ref="H89:O89"/>
+    <mergeCell ref="G90:G127"/>
+    <mergeCell ref="H28:O28"/>
+    <mergeCell ref="G29:G85"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
